--- a/jj易教何子全python/project/20260530/附注_合并项目注释_完整格式1.xlsx
+++ b/jj易教何子全python/project/20260530/附注_合并项目注释_完整格式1.xlsx
@@ -226,35 +226,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -777,11 +791,11 @@
           <t>按组合计提坏账准备的应收账款</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr"/>
-      <c r="C14" s="13" t="inlineStr"/>
-      <c r="D14" s="13" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="15" t="inlineStr"/>
+      <c r="B14" s="18" t="inlineStr"/>
+      <c r="C14" s="18" t="inlineStr"/>
+      <c r="D14" s="18" t="inlineStr"/>
+      <c r="E14" s="18" t="inlineStr"/>
+      <c r="F14" s="19" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -795,8 +809,8 @@
       <c r="C15" s="6" t="n">
         <v>60.28</v>
       </c>
-      <c r="D15" s="13" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr"/>
+      <c r="D15" s="18" t="inlineStr"/>
+      <c r="E15" s="18" t="inlineStr"/>
       <c r="F15" s="7" t="n">
         <v>4078882.27</v>
       </c>
@@ -807,11 +821,11 @@
           <t>组合2：备用金、押金</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr"/>
-      <c r="C16" s="13" t="inlineStr"/>
-      <c r="D16" s="13" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="15" t="inlineStr"/>
+      <c r="B16" s="18" t="inlineStr"/>
+      <c r="C16" s="18" t="inlineStr"/>
+      <c r="D16" s="18" t="inlineStr"/>
+      <c r="E16" s="18" t="inlineStr"/>
+      <c r="F16" s="19" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -825,8 +839,8 @@
       <c r="C17" s="6" t="n">
         <v>39.72</v>
       </c>
-      <c r="D17" s="13" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr"/>
+      <c r="D17" s="18" t="inlineStr"/>
+      <c r="E17" s="18" t="inlineStr"/>
       <c r="F17" s="7" t="n">
         <v>2687747.69</v>
       </c>
@@ -840,11 +854,11 @@
       <c r="B18" s="9" t="n">
         <v>6766629.96</v>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D18" s="19" t="inlineStr"/>
-      <c r="E18" s="19" t="inlineStr"/>
+      <c r="D18" s="21" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr"/>
       <c r="F18" s="10" t="n">
         <v>6766629.96</v>
       </c>
@@ -922,11 +936,11 @@
           <t>按组合计提坏账准备的应收账款</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr"/>
-      <c r="C24" s="13" t="inlineStr"/>
-      <c r="D24" s="13" t="inlineStr"/>
-      <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="15" t="inlineStr"/>
+      <c r="B24" s="18" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr"/>
+      <c r="D24" s="18" t="inlineStr"/>
+      <c r="E24" s="18" t="inlineStr"/>
+      <c r="F24" s="19" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -937,11 +951,11 @@
       <c r="B25" s="6" t="n">
         <v>7532517.01</v>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="22" t="n">
         <v>98</v>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr"/>
+      <c r="D25" s="18" t="inlineStr"/>
+      <c r="E25" s="18" t="inlineStr"/>
       <c r="F25" s="7" t="n">
         <v>7532517.01</v>
       </c>
@@ -952,11 +966,11 @@
           <t>组合2：备用金、押金</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr"/>
-      <c r="C26" s="13" t="inlineStr"/>
-      <c r="D26" s="13" t="inlineStr"/>
-      <c r="E26" s="13" t="inlineStr"/>
-      <c r="F26" s="15" t="inlineStr"/>
+      <c r="B26" s="18" t="inlineStr"/>
+      <c r="C26" s="18" t="inlineStr"/>
+      <c r="D26" s="18" t="inlineStr"/>
+      <c r="E26" s="18" t="inlineStr"/>
+      <c r="F26" s="19" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -967,11 +981,11 @@
       <c r="B27" s="6" t="n">
         <v>154060.8</v>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr"/>
+      <c r="D27" s="18" t="inlineStr"/>
+      <c r="E27" s="18" t="inlineStr"/>
       <c r="F27" s="7" t="n">
         <v>154060.8</v>
       </c>
@@ -985,11 +999,11 @@
       <c r="B28" s="9" t="n">
         <v>7686577.81</v>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C28" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D28" s="19" t="inlineStr"/>
-      <c r="E28" s="19" t="inlineStr"/>
+      <c r="D28" s="23" t="inlineStr"/>
+      <c r="E28" s="23" t="inlineStr"/>
       <c r="F28" s="10" t="n">
         <v>7686577.81</v>
       </c>
@@ -1095,7 +1109,7 @@
       <c r="C38" s="6" t="n">
         <v>58.84</v>
       </c>
-      <c r="D38" s="15" t="inlineStr"/>
+      <c r="D38" s="19" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -1109,7 +1123,7 @@
       <c r="C39" s="6" t="n">
         <v>36.13</v>
       </c>
-      <c r="D39" s="15" t="inlineStr"/>
+      <c r="D39" s="19" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1117,13 +1131,13 @@
           <t>深圳市中小担商业保理有限公司</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n">
+      <c r="B40" s="22" t="n">
         <v>146000</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>2.16</v>
       </c>
-      <c r="D40" s="15" t="inlineStr"/>
+      <c r="D40" s="19" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1137,7 +1151,7 @@
       <c r="C41" s="6" t="n">
         <v>1.44</v>
       </c>
-      <c r="D41" s="15" t="inlineStr"/>
+      <c r="D41" s="19" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1151,7 +1165,7 @@
       <c r="C42" s="6" t="n">
         <v>1.43</v>
       </c>
-      <c r="D42" s="15" t="inlineStr"/>
+      <c r="D42" s="19" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -1162,10 +1176,10 @@
       <c r="B43" s="9" t="n">
         <v>6766629.96</v>
       </c>
-      <c r="C43" s="18" t="n">
+      <c r="C43" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D43" s="21" t="inlineStr"/>
+      <c r="D43" s="24" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1199,7 +1213,7 @@
           <t>期末余额</t>
         </is>
       </c>
-      <c r="C48" s="22" t="n"/>
+      <c r="C48" s="25" t="n"/>
       <c r="D48" s="4" t="inlineStr">
         <is>
           <t>期初余额</t>
@@ -1239,13 +1253,13 @@
       <c r="B50" s="6" t="n">
         <v>4093944.05</v>
       </c>
-      <c r="C50" s="20" t="n">
+      <c r="C50" s="22" t="n">
         <v>100</v>
       </c>
       <c r="D50" s="6" t="n">
         <v>346812.92</v>
       </c>
-      <c r="E50" s="23" t="n">
+      <c r="E50" s="26" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1258,13 +1272,13 @@
       <c r="B51" s="9" t="n">
         <v>4093944.05</v>
       </c>
-      <c r="C51" s="18" t="n">
+      <c r="C51" s="20" t="n">
         <v>100</v>
       </c>
       <c r="D51" s="9" t="n">
         <v>346812.92</v>
       </c>
-      <c r="E51" s="24" t="n">
+      <c r="E51" s="27" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1308,10 +1322,10 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B55" s="20" t="n">
+      <c r="B55" s="22" t="n">
         <v>4034920</v>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="18" t="inlineStr">
         <is>
           <t>1年以内</t>
         </is>
@@ -1319,7 +1333,7 @@
       <c r="D55" s="6" t="n">
         <v>98.56</v>
       </c>
-      <c r="E55" s="15" t="inlineStr">
+      <c r="E55" s="19" t="inlineStr">
         <is>
           <t>委托研发费</t>
         </is>
@@ -1334,7 +1348,7 @@
       <c r="B56" s="6" t="n">
         <v>59024.05</v>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>1年以内</t>
         </is>
@@ -1342,7 +1356,7 @@
       <c r="D56" s="6" t="n">
         <v>1.44</v>
       </c>
-      <c r="E56" s="15" t="inlineStr">
+      <c r="E56" s="19" t="inlineStr">
         <is>
           <t>服务款</t>
         </is>
@@ -1357,11 +1371,11 @@
       <c r="B57" s="9" t="n">
         <v>4093944.05</v>
       </c>
-      <c r="C57" s="19" t="inlineStr"/>
-      <c r="D57" s="18" t="n">
+      <c r="C57" s="23" t="inlineStr"/>
+      <c r="D57" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="E57" s="21" t="inlineStr"/>
+      <c r="E57" s="24" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1396,7 +1410,7 @@
         </is>
       </c>
       <c r="C62" s="11" t="n"/>
-      <c r="D62" s="22" t="n"/>
+      <c r="D62" s="25" t="n"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
           <t>期初余额</t>
@@ -1444,12 +1458,12 @@
           <t>应收利息</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr"/>
-      <c r="C64" s="13" t="inlineStr"/>
-      <c r="D64" s="13" t="inlineStr"/>
-      <c r="E64" s="13" t="inlineStr"/>
-      <c r="F64" s="13" t="inlineStr"/>
-      <c r="G64" s="15" t="inlineStr"/>
+      <c r="B64" s="18" t="inlineStr"/>
+      <c r="C64" s="18" t="inlineStr"/>
+      <c r="D64" s="18" t="inlineStr"/>
+      <c r="E64" s="18" t="inlineStr"/>
+      <c r="F64" s="18" t="inlineStr"/>
+      <c r="G64" s="19" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -1457,12 +1471,12 @@
           <t>应收股利</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr"/>
-      <c r="C65" s="13" t="inlineStr"/>
-      <c r="D65" s="13" t="inlineStr"/>
-      <c r="E65" s="13" t="inlineStr"/>
-      <c r="F65" s="13" t="inlineStr"/>
-      <c r="G65" s="15" t="inlineStr"/>
+      <c r="B65" s="18" t="inlineStr"/>
+      <c r="C65" s="18" t="inlineStr"/>
+      <c r="D65" s="18" t="inlineStr"/>
+      <c r="E65" s="18" t="inlineStr"/>
+      <c r="F65" s="18" t="inlineStr"/>
+      <c r="G65" s="19" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -1473,14 +1487,14 @@
       <c r="B66" s="6" t="n">
         <v>256225.13</v>
       </c>
-      <c r="C66" s="13" t="inlineStr"/>
+      <c r="C66" s="18" t="inlineStr"/>
       <c r="D66" s="6" t="n">
         <v>256225.13</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>1403120.36</v>
       </c>
-      <c r="F66" s="13" t="inlineStr"/>
+      <c r="F66" s="18" t="inlineStr"/>
       <c r="G66" s="7" t="n">
         <v>1403120.36</v>
       </c>
@@ -1494,14 +1508,14 @@
       <c r="B67" s="9" t="n">
         <v>256225.13</v>
       </c>
-      <c r="C67" s="19" t="inlineStr"/>
+      <c r="C67" s="21" t="inlineStr"/>
       <c r="D67" s="9" t="n">
         <v>256225.13</v>
       </c>
       <c r="E67" s="9" t="n">
         <v>1403120.36</v>
       </c>
-      <c r="F67" s="19" t="inlineStr"/>
+      <c r="F67" s="21" t="inlineStr"/>
       <c r="G67" s="10" t="n">
         <v>1403120.36</v>
       </c>
@@ -1532,7 +1546,7 @@
         </is>
       </c>
       <c r="C71" s="11" t="n"/>
-      <c r="D71" s="22" t="n"/>
+      <c r="D71" s="25" t="n"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
           <t>期初余额</t>
@@ -1583,14 +1597,14 @@
       <c r="B73" s="6" t="n">
         <v>170853.53</v>
       </c>
-      <c r="C73" s="13" t="inlineStr"/>
+      <c r="C73" s="18" t="inlineStr"/>
       <c r="D73" s="6" t="n">
         <v>170853.53</v>
       </c>
       <c r="E73" s="6" t="n">
         <v>1317748.76</v>
       </c>
-      <c r="F73" s="13" t="inlineStr"/>
+      <c r="F73" s="18" t="inlineStr"/>
       <c r="G73" s="7" t="n">
         <v>1317748.76</v>
       </c>
@@ -1601,12 +1615,12 @@
           <t>1-2年</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr"/>
-      <c r="C74" s="13" t="inlineStr"/>
-      <c r="D74" s="13" t="inlineStr"/>
-      <c r="E74" s="13" t="inlineStr"/>
-      <c r="F74" s="13" t="inlineStr"/>
-      <c r="G74" s="15" t="inlineStr"/>
+      <c r="B74" s="18" t="inlineStr"/>
+      <c r="C74" s="18" t="inlineStr"/>
+      <c r="D74" s="18" t="inlineStr"/>
+      <c r="E74" s="18" t="inlineStr"/>
+      <c r="F74" s="18" t="inlineStr"/>
+      <c r="G74" s="19" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -1614,13 +1628,13 @@
           <t>2-3年</t>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr"/>
-      <c r="C75" s="13" t="inlineStr"/>
-      <c r="D75" s="13" t="inlineStr"/>
+      <c r="B75" s="18" t="inlineStr"/>
+      <c r="C75" s="18" t="inlineStr"/>
+      <c r="D75" s="18" t="inlineStr"/>
       <c r="E75" s="6" t="n">
         <v>81171.60000000001</v>
       </c>
-      <c r="F75" s="13" t="inlineStr"/>
+      <c r="F75" s="18" t="inlineStr"/>
       <c r="G75" s="7" t="n">
         <v>81171.60000000001</v>
       </c>
@@ -1634,13 +1648,13 @@
       <c r="B76" s="6" t="n">
         <v>81171.60000000001</v>
       </c>
-      <c r="C76" s="13" t="inlineStr"/>
+      <c r="C76" s="18" t="inlineStr"/>
       <c r="D76" s="6" t="n">
         <v>81171.60000000001</v>
       </c>
-      <c r="E76" s="13" t="inlineStr"/>
-      <c r="F76" s="13" t="inlineStr"/>
-      <c r="G76" s="15" t="inlineStr"/>
+      <c r="E76" s="18" t="inlineStr"/>
+      <c r="F76" s="18" t="inlineStr"/>
+      <c r="G76" s="19" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -1648,14 +1662,14 @@
           <t>4-5年</t>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr"/>
-      <c r="C77" s="13" t="inlineStr"/>
-      <c r="D77" s="13" t="inlineStr"/>
-      <c r="E77" s="20" t="n">
+      <c r="B77" s="18" t="inlineStr"/>
+      <c r="C77" s="18" t="inlineStr"/>
+      <c r="D77" s="18" t="inlineStr"/>
+      <c r="E77" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="F77" s="13" t="inlineStr"/>
-      <c r="G77" s="23" t="n">
+      <c r="F77" s="18" t="inlineStr"/>
+      <c r="G77" s="26" t="n">
         <v>4200</v>
       </c>
     </row>
@@ -1665,16 +1679,16 @@
           <t>5年以上</t>
         </is>
       </c>
-      <c r="B78" s="20" t="n">
+      <c r="B78" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="C78" s="13" t="inlineStr"/>
-      <c r="D78" s="20" t="n">
+      <c r="C78" s="18" t="inlineStr"/>
+      <c r="D78" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="E78" s="13" t="inlineStr"/>
-      <c r="F78" s="13" t="inlineStr"/>
-      <c r="G78" s="15" t="inlineStr"/>
+      <c r="E78" s="18" t="inlineStr"/>
+      <c r="F78" s="18" t="inlineStr"/>
+      <c r="G78" s="19" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -1685,14 +1699,14 @@
       <c r="B79" s="9" t="n">
         <v>256225.13</v>
       </c>
-      <c r="C79" s="19" t="inlineStr"/>
+      <c r="C79" s="21" t="inlineStr"/>
       <c r="D79" s="9" t="n">
         <v>256225.13</v>
       </c>
       <c r="E79" s="9" t="n">
         <v>1403120.36</v>
       </c>
-      <c r="F79" s="19" t="inlineStr"/>
+      <c r="F79" s="21" t="inlineStr"/>
       <c r="G79" s="10" t="n">
         <v>1403120.36</v>
       </c>
@@ -1759,10 +1773,10 @@
           <t>期初余额</t>
         </is>
       </c>
-      <c r="B84" s="13" t="inlineStr"/>
-      <c r="C84" s="13" t="inlineStr"/>
-      <c r="D84" s="13" t="inlineStr"/>
-      <c r="E84" s="15" t="inlineStr"/>
+      <c r="B84" s="18" t="inlineStr"/>
+      <c r="C84" s="18" t="inlineStr"/>
+      <c r="D84" s="18" t="inlineStr"/>
+      <c r="E84" s="19" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -1770,10 +1784,10 @@
           <t>转入第二阶段</t>
         </is>
       </c>
-      <c r="B85" s="13" t="inlineStr"/>
-      <c r="C85" s="13" t="inlineStr"/>
-      <c r="D85" s="13" t="inlineStr"/>
-      <c r="E85" s="15" t="inlineStr"/>
+      <c r="B85" s="18" t="inlineStr"/>
+      <c r="C85" s="18" t="inlineStr"/>
+      <c r="D85" s="18" t="inlineStr"/>
+      <c r="E85" s="19" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -1781,10 +1795,10 @@
           <t>转入第三阶段</t>
         </is>
       </c>
-      <c r="B86" s="13" t="inlineStr"/>
-      <c r="C86" s="13" t="inlineStr"/>
-      <c r="D86" s="13" t="inlineStr"/>
-      <c r="E86" s="15" t="inlineStr"/>
+      <c r="B86" s="18" t="inlineStr"/>
+      <c r="C86" s="18" t="inlineStr"/>
+      <c r="D86" s="18" t="inlineStr"/>
+      <c r="E86" s="19" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -1792,10 +1806,10 @@
           <t>转回第二阶段</t>
         </is>
       </c>
-      <c r="B87" s="13" t="inlineStr"/>
-      <c r="C87" s="13" t="inlineStr"/>
-      <c r="D87" s="13" t="inlineStr"/>
-      <c r="E87" s="15" t="inlineStr"/>
+      <c r="B87" s="18" t="inlineStr"/>
+      <c r="C87" s="18" t="inlineStr"/>
+      <c r="D87" s="18" t="inlineStr"/>
+      <c r="E87" s="19" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -1803,10 +1817,10 @@
           <t>转回第一阶段</t>
         </is>
       </c>
-      <c r="B88" s="13" t="inlineStr"/>
-      <c r="C88" s="13" t="inlineStr"/>
-      <c r="D88" s="13" t="inlineStr"/>
-      <c r="E88" s="15" t="inlineStr"/>
+      <c r="B88" s="18" t="inlineStr"/>
+      <c r="C88" s="18" t="inlineStr"/>
+      <c r="D88" s="18" t="inlineStr"/>
+      <c r="E88" s="19" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -1814,10 +1828,10 @@
           <t>本期计提</t>
         </is>
       </c>
-      <c r="B89" s="13" t="inlineStr"/>
-      <c r="C89" s="13" t="inlineStr"/>
-      <c r="D89" s="13" t="inlineStr"/>
-      <c r="E89" s="15" t="inlineStr"/>
+      <c r="B89" s="18" t="inlineStr"/>
+      <c r="C89" s="18" t="inlineStr"/>
+      <c r="D89" s="18" t="inlineStr"/>
+      <c r="E89" s="19" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -1825,10 +1839,10 @@
           <t>其他变动</t>
         </is>
       </c>
-      <c r="B90" s="13" t="inlineStr"/>
-      <c r="C90" s="13" t="inlineStr"/>
-      <c r="D90" s="13" t="inlineStr"/>
-      <c r="E90" s="15" t="inlineStr"/>
+      <c r="B90" s="18" t="inlineStr"/>
+      <c r="C90" s="18" t="inlineStr"/>
+      <c r="D90" s="18" t="inlineStr"/>
+      <c r="E90" s="19" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -1836,10 +1850,10 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B91" s="19" t="inlineStr"/>
-      <c r="C91" s="19" t="inlineStr"/>
-      <c r="D91" s="19" t="inlineStr"/>
-      <c r="E91" s="21" t="inlineStr"/>
+      <c r="B91" s="21" t="inlineStr"/>
+      <c r="C91" s="21" t="inlineStr"/>
+      <c r="D91" s="21" t="inlineStr"/>
+      <c r="E91" s="24" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1885,8 +1899,8 @@
           <t>往来款</t>
         </is>
       </c>
-      <c r="B97" s="13" t="inlineStr"/>
-      <c r="C97" s="23" t="n">
+      <c r="B97" s="18" t="inlineStr"/>
+      <c r="C97" s="26" t="n">
         <v>1207840</v>
       </c>
     </row>
@@ -1975,25 +1989,25 @@
           <t>资金部/王冠</t>
         </is>
       </c>
-      <c r="B104" s="13" t="inlineStr">
+      <c r="B104" s="18" t="inlineStr">
         <is>
           <t>备用金</t>
         </is>
       </c>
-      <c r="C104" s="20" t="n">
+      <c r="C104" s="22" t="n">
         <v>100000</v>
       </c>
-      <c r="D104" s="13" t="inlineStr">
+      <c r="D104" s="18" t="inlineStr">
         <is>
           <t>1年以内</t>
         </is>
       </c>
-      <c r="E104" s="13" t="inlineStr">
+      <c r="E104" s="18" t="inlineStr">
         <is>
           <t>39.03%</t>
         </is>
       </c>
-      <c r="F104" s="15" t="inlineStr"/>
+      <c r="F104" s="19" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -2001,7 +2015,7 @@
           <t>华润置地前海有限公司</t>
         </is>
       </c>
-      <c r="B105" s="13" t="inlineStr">
+      <c r="B105" s="18" t="inlineStr">
         <is>
           <t>押金</t>
         </is>
@@ -2009,17 +2023,17 @@
       <c r="C105" s="6" t="n">
         <v>81171.60000000001</v>
       </c>
-      <c r="D105" s="13" t="inlineStr">
+      <c r="D105" s="18" t="inlineStr">
         <is>
           <t>3-4年</t>
         </is>
       </c>
-      <c r="E105" s="13" t="inlineStr">
+      <c r="E105" s="18" t="inlineStr">
         <is>
           <t>31.68%</t>
         </is>
       </c>
-      <c r="F105" s="15" t="inlineStr"/>
+      <c r="F105" s="19" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
@@ -2027,13 +2041,13 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B106" s="19" t="inlineStr"/>
+      <c r="B106" s="21" t="inlineStr"/>
       <c r="C106" s="9" t="n">
         <v>181171.6</v>
       </c>
-      <c r="D106" s="19" t="inlineStr"/>
-      <c r="E106" s="19" t="inlineStr"/>
-      <c r="F106" s="21" t="inlineStr"/>
+      <c r="D106" s="21" t="inlineStr"/>
+      <c r="E106" s="21" t="inlineStr"/>
+      <c r="F106" s="24" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2111,7 +2125,7 @@
         </is>
       </c>
       <c r="C115" s="11" t="n"/>
-      <c r="D115" s="22" t="n"/>
+      <c r="D115" s="25" t="n"/>
       <c r="E115" s="4" t="inlineStr">
         <is>
           <t>期初余额</t>
@@ -2162,14 +2176,14 @@
       <c r="B117" s="6" t="n">
         <v>16800783.93</v>
       </c>
-      <c r="C117" s="13" t="inlineStr"/>
+      <c r="C117" s="18" t="inlineStr"/>
       <c r="D117" s="6" t="n">
         <v>16800783.93</v>
       </c>
       <c r="E117" s="6" t="n">
         <v>6800783.93</v>
       </c>
-      <c r="F117" s="13" t="inlineStr"/>
+      <c r="F117" s="18" t="inlineStr"/>
       <c r="G117" s="7" t="n">
         <v>6800783.93</v>
       </c>
@@ -2183,14 +2197,14 @@
       <c r="B118" s="9" t="n">
         <v>16800783.93</v>
       </c>
-      <c r="C118" s="19" t="inlineStr"/>
+      <c r="C118" s="21" t="inlineStr"/>
       <c r="D118" s="9" t="n">
         <v>16800783.93</v>
       </c>
       <c r="E118" s="9" t="n">
         <v>6800783.93</v>
       </c>
-      <c r="F118" s="19" t="inlineStr"/>
+      <c r="F118" s="21" t="inlineStr"/>
       <c r="G118" s="10" t="n">
         <v>6800783.93</v>
       </c>
@@ -2248,15 +2262,15 @@
       <c r="B122" s="6" t="n">
         <v>6800783.93</v>
       </c>
-      <c r="C122" s="20" t="n">
+      <c r="C122" s="22" t="n">
         <v>10000000</v>
       </c>
-      <c r="D122" s="13" t="inlineStr"/>
+      <c r="D122" s="18" t="inlineStr"/>
       <c r="E122" s="6" t="n">
         <v>16800783.93</v>
       </c>
-      <c r="F122" s="13" t="inlineStr"/>
-      <c r="G122" s="15" t="inlineStr"/>
+      <c r="F122" s="18" t="inlineStr"/>
+      <c r="G122" s="19" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -2267,15 +2281,15 @@
       <c r="B123" s="9" t="n">
         <v>6800783.93</v>
       </c>
-      <c r="C123" s="18" t="n">
+      <c r="C123" s="20" t="n">
         <v>10000000</v>
       </c>
-      <c r="D123" s="19" t="inlineStr"/>
+      <c r="D123" s="21" t="inlineStr"/>
       <c r="E123" s="9" t="n">
         <v>16800783.93</v>
       </c>
-      <c r="F123" s="19" t="inlineStr"/>
-      <c r="G123" s="21" t="inlineStr"/>
+      <c r="F123" s="21" t="inlineStr"/>
+      <c r="G123" s="24" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -2327,8 +2341,8 @@
           <t>固定资产清理</t>
         </is>
       </c>
-      <c r="B129" s="13" t="inlineStr"/>
-      <c r="C129" s="15" t="inlineStr"/>
+      <c r="B129" s="18" t="inlineStr"/>
+      <c r="C129" s="19" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
@@ -2383,16 +2397,16 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
+      <c r="A134" s="28" t="inlineStr">
         <is>
           <t>一、账面原值</t>
         </is>
       </c>
-      <c r="B134" s="13" t="inlineStr"/>
-      <c r="C134" s="13" t="inlineStr"/>
-      <c r="D134" s="13" t="inlineStr"/>
-      <c r="E134" s="13" t="inlineStr"/>
-      <c r="F134" s="15" t="inlineStr"/>
+      <c r="B134" s="18" t="inlineStr"/>
+      <c r="C134" s="18" t="inlineStr"/>
+      <c r="D134" s="18" t="inlineStr"/>
+      <c r="E134" s="18" t="inlineStr"/>
+      <c r="F134" s="19" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -2422,11 +2436,11 @@
           <t>2、本期增加金额</t>
         </is>
       </c>
-      <c r="B136" s="13" t="inlineStr"/>
-      <c r="C136" s="13" t="inlineStr"/>
-      <c r="D136" s="13" t="inlineStr"/>
-      <c r="E136" s="13" t="inlineStr"/>
-      <c r="F136" s="15" t="inlineStr"/>
+      <c r="B136" s="18" t="inlineStr"/>
+      <c r="C136" s="18" t="inlineStr"/>
+      <c r="D136" s="18" t="inlineStr"/>
+      <c r="E136" s="18" t="inlineStr"/>
+      <c r="F136" s="19" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -2434,11 +2448,11 @@
           <t>(1)购置</t>
         </is>
       </c>
-      <c r="B137" s="13" t="inlineStr"/>
-      <c r="C137" s="13" t="inlineStr"/>
-      <c r="D137" s="13" t="inlineStr"/>
-      <c r="E137" s="13" t="inlineStr"/>
-      <c r="F137" s="15" t="inlineStr"/>
+      <c r="B137" s="18" t="inlineStr"/>
+      <c r="C137" s="18" t="inlineStr"/>
+      <c r="D137" s="18" t="inlineStr"/>
+      <c r="E137" s="18" t="inlineStr"/>
+      <c r="F137" s="19" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -2446,11 +2460,11 @@
           <t>(2)融资租赁增加</t>
         </is>
       </c>
-      <c r="B138" s="13" t="inlineStr"/>
-      <c r="C138" s="13" t="inlineStr"/>
-      <c r="D138" s="13" t="inlineStr"/>
-      <c r="E138" s="13" t="inlineStr"/>
-      <c r="F138" s="15" t="inlineStr"/>
+      <c r="B138" s="18" t="inlineStr"/>
+      <c r="C138" s="18" t="inlineStr"/>
+      <c r="D138" s="18" t="inlineStr"/>
+      <c r="E138" s="18" t="inlineStr"/>
+      <c r="F138" s="19" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -2458,11 +2472,11 @@
           <t>3、本期减少金额</t>
         </is>
       </c>
-      <c r="B139" s="13" t="inlineStr"/>
-      <c r="C139" s="13" t="inlineStr"/>
-      <c r="D139" s="13" t="inlineStr"/>
-      <c r="E139" s="13" t="inlineStr"/>
-      <c r="F139" s="15" t="inlineStr"/>
+      <c r="B139" s="18" t="inlineStr"/>
+      <c r="C139" s="18" t="inlineStr"/>
+      <c r="D139" s="18" t="inlineStr"/>
+      <c r="E139" s="18" t="inlineStr"/>
+      <c r="F139" s="19" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -2470,11 +2484,11 @@
           <t>(1)处置或报废</t>
         </is>
       </c>
-      <c r="B140" s="13" t="inlineStr"/>
-      <c r="C140" s="13" t="inlineStr"/>
-      <c r="D140" s="13" t="inlineStr"/>
-      <c r="E140" s="13" t="inlineStr"/>
-      <c r="F140" s="15" t="inlineStr"/>
+      <c r="B140" s="18" t="inlineStr"/>
+      <c r="C140" s="18" t="inlineStr"/>
+      <c r="D140" s="18" t="inlineStr"/>
+      <c r="E140" s="18" t="inlineStr"/>
+      <c r="F140" s="19" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -2482,11 +2496,11 @@
           <t>(2) 融资租赁减少</t>
         </is>
       </c>
-      <c r="B141" s="13" t="inlineStr"/>
-      <c r="C141" s="13" t="inlineStr"/>
-      <c r="D141" s="13" t="inlineStr"/>
-      <c r="E141" s="13" t="inlineStr"/>
-      <c r="F141" s="15" t="inlineStr"/>
+      <c r="B141" s="18" t="inlineStr"/>
+      <c r="C141" s="18" t="inlineStr"/>
+      <c r="D141" s="18" t="inlineStr"/>
+      <c r="E141" s="18" t="inlineStr"/>
+      <c r="F141" s="19" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -2511,16 +2525,16 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
+      <c r="A143" s="28" t="inlineStr">
         <is>
           <t>二、累计折旧</t>
         </is>
       </c>
-      <c r="B143" s="13" t="inlineStr"/>
-      <c r="C143" s="13" t="inlineStr"/>
-      <c r="D143" s="13" t="inlineStr"/>
-      <c r="E143" s="13" t="inlineStr"/>
-      <c r="F143" s="15" t="inlineStr"/>
+      <c r="B143" s="18" t="inlineStr"/>
+      <c r="C143" s="18" t="inlineStr"/>
+      <c r="D143" s="18" t="inlineStr"/>
+      <c r="E143" s="18" t="inlineStr"/>
+      <c r="F143" s="19" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -2594,11 +2608,11 @@
           <t>(2) 融资租赁增加</t>
         </is>
       </c>
-      <c r="B147" s="13" t="inlineStr"/>
-      <c r="C147" s="13" t="inlineStr"/>
-      <c r="D147" s="13" t="inlineStr"/>
-      <c r="E147" s="13" t="inlineStr"/>
-      <c r="F147" s="15" t="inlineStr"/>
+      <c r="B147" s="18" t="inlineStr"/>
+      <c r="C147" s="18" t="inlineStr"/>
+      <c r="D147" s="18" t="inlineStr"/>
+      <c r="E147" s="18" t="inlineStr"/>
+      <c r="F147" s="19" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -2606,11 +2620,11 @@
           <t>3、本期减少金额</t>
         </is>
       </c>
-      <c r="B148" s="13" t="inlineStr"/>
-      <c r="C148" s="13" t="inlineStr"/>
-      <c r="D148" s="13" t="inlineStr"/>
-      <c r="E148" s="13" t="inlineStr"/>
-      <c r="F148" s="15" t="inlineStr"/>
+      <c r="B148" s="18" t="inlineStr"/>
+      <c r="C148" s="18" t="inlineStr"/>
+      <c r="D148" s="18" t="inlineStr"/>
+      <c r="E148" s="18" t="inlineStr"/>
+      <c r="F148" s="19" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -2618,11 +2632,11 @@
           <t>(1)处置或报废</t>
         </is>
       </c>
-      <c r="B149" s="13" t="inlineStr"/>
-      <c r="C149" s="13" t="inlineStr"/>
-      <c r="D149" s="13" t="inlineStr"/>
-      <c r="E149" s="13" t="inlineStr"/>
-      <c r="F149" s="15" t="inlineStr"/>
+      <c r="B149" s="18" t="inlineStr"/>
+      <c r="C149" s="18" t="inlineStr"/>
+      <c r="D149" s="18" t="inlineStr"/>
+      <c r="E149" s="18" t="inlineStr"/>
+      <c r="F149" s="19" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -2630,11 +2644,11 @@
           <t>(2) 融资租赁减少</t>
         </is>
       </c>
-      <c r="B150" s="13" t="inlineStr"/>
-      <c r="C150" s="13" t="inlineStr"/>
-      <c r="D150" s="13" t="inlineStr"/>
-      <c r="E150" s="13" t="inlineStr"/>
-      <c r="F150" s="15" t="inlineStr"/>
+      <c r="B150" s="18" t="inlineStr"/>
+      <c r="C150" s="18" t="inlineStr"/>
+      <c r="D150" s="18" t="inlineStr"/>
+      <c r="E150" s="18" t="inlineStr"/>
+      <c r="F150" s="19" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -2659,16 +2673,16 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
+      <c r="A152" s="28" t="inlineStr">
         <is>
           <t>三、减值准备</t>
         </is>
       </c>
-      <c r="B152" s="13" t="inlineStr"/>
-      <c r="C152" s="13" t="inlineStr"/>
-      <c r="D152" s="13" t="inlineStr"/>
-      <c r="E152" s="13" t="inlineStr"/>
-      <c r="F152" s="15" t="inlineStr"/>
+      <c r="B152" s="18" t="inlineStr"/>
+      <c r="C152" s="18" t="inlineStr"/>
+      <c r="D152" s="18" t="inlineStr"/>
+      <c r="E152" s="18" t="inlineStr"/>
+      <c r="F152" s="19" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -2676,11 +2690,11 @@
           <t>1、期初余额</t>
         </is>
       </c>
-      <c r="B153" s="13" t="inlineStr"/>
-      <c r="C153" s="13" t="inlineStr"/>
-      <c r="D153" s="13" t="inlineStr"/>
-      <c r="E153" s="13" t="inlineStr"/>
-      <c r="F153" s="15" t="inlineStr"/>
+      <c r="B153" s="18" t="inlineStr"/>
+      <c r="C153" s="18" t="inlineStr"/>
+      <c r="D153" s="18" t="inlineStr"/>
+      <c r="E153" s="18" t="inlineStr"/>
+      <c r="F153" s="19" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -2688,11 +2702,11 @@
           <t>2、本期增加金额</t>
         </is>
       </c>
-      <c r="B154" s="13" t="inlineStr"/>
-      <c r="C154" s="13" t="inlineStr"/>
-      <c r="D154" s="13" t="inlineStr"/>
-      <c r="E154" s="13" t="inlineStr"/>
-      <c r="F154" s="15" t="inlineStr"/>
+      <c r="B154" s="18" t="inlineStr"/>
+      <c r="C154" s="18" t="inlineStr"/>
+      <c r="D154" s="18" t="inlineStr"/>
+      <c r="E154" s="18" t="inlineStr"/>
+      <c r="F154" s="19" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -2700,11 +2714,11 @@
           <t>(1)计提</t>
         </is>
       </c>
-      <c r="B155" s="13" t="inlineStr"/>
-      <c r="C155" s="13" t="inlineStr"/>
-      <c r="D155" s="13" t="inlineStr"/>
-      <c r="E155" s="13" t="inlineStr"/>
-      <c r="F155" s="15" t="inlineStr"/>
+      <c r="B155" s="18" t="inlineStr"/>
+      <c r="C155" s="18" t="inlineStr"/>
+      <c r="D155" s="18" t="inlineStr"/>
+      <c r="E155" s="18" t="inlineStr"/>
+      <c r="F155" s="19" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -2712,11 +2726,11 @@
           <t>(2) 融资租赁增加</t>
         </is>
       </c>
-      <c r="B156" s="13" t="inlineStr"/>
-      <c r="C156" s="13" t="inlineStr"/>
-      <c r="D156" s="13" t="inlineStr"/>
-      <c r="E156" s="13" t="inlineStr"/>
-      <c r="F156" s="15" t="inlineStr"/>
+      <c r="B156" s="18" t="inlineStr"/>
+      <c r="C156" s="18" t="inlineStr"/>
+      <c r="D156" s="18" t="inlineStr"/>
+      <c r="E156" s="18" t="inlineStr"/>
+      <c r="F156" s="19" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -2724,11 +2738,11 @@
           <t>3、本期减少金额</t>
         </is>
       </c>
-      <c r="B157" s="13" t="inlineStr"/>
-      <c r="C157" s="13" t="inlineStr"/>
-      <c r="D157" s="13" t="inlineStr"/>
-      <c r="E157" s="13" t="inlineStr"/>
-      <c r="F157" s="15" t="inlineStr"/>
+      <c r="B157" s="18" t="inlineStr"/>
+      <c r="C157" s="18" t="inlineStr"/>
+      <c r="D157" s="18" t="inlineStr"/>
+      <c r="E157" s="18" t="inlineStr"/>
+      <c r="F157" s="19" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -2736,11 +2750,11 @@
           <t>(1)处置或报废</t>
         </is>
       </c>
-      <c r="B158" s="13" t="inlineStr"/>
-      <c r="C158" s="13" t="inlineStr"/>
-      <c r="D158" s="13" t="inlineStr"/>
-      <c r="E158" s="13" t="inlineStr"/>
-      <c r="F158" s="15" t="inlineStr"/>
+      <c r="B158" s="18" t="inlineStr"/>
+      <c r="C158" s="18" t="inlineStr"/>
+      <c r="D158" s="18" t="inlineStr"/>
+      <c r="E158" s="18" t="inlineStr"/>
+      <c r="F158" s="19" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -2748,11 +2762,11 @@
           <t>(2) 融资租赁减少</t>
         </is>
       </c>
-      <c r="B159" s="13" t="inlineStr"/>
-      <c r="C159" s="13" t="inlineStr"/>
-      <c r="D159" s="13" t="inlineStr"/>
-      <c r="E159" s="13" t="inlineStr"/>
-      <c r="F159" s="15" t="inlineStr"/>
+      <c r="B159" s="18" t="inlineStr"/>
+      <c r="C159" s="18" t="inlineStr"/>
+      <c r="D159" s="18" t="inlineStr"/>
+      <c r="E159" s="18" t="inlineStr"/>
+      <c r="F159" s="19" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -2760,23 +2774,23 @@
           <t>4、期末余额</t>
         </is>
       </c>
-      <c r="B160" s="13" t="inlineStr"/>
-      <c r="C160" s="13" t="inlineStr"/>
-      <c r="D160" s="13" t="inlineStr"/>
-      <c r="E160" s="13" t="inlineStr"/>
-      <c r="F160" s="15" t="inlineStr"/>
+      <c r="B160" s="18" t="inlineStr"/>
+      <c r="C160" s="18" t="inlineStr"/>
+      <c r="D160" s="18" t="inlineStr"/>
+      <c r="E160" s="18" t="inlineStr"/>
+      <c r="F160" s="19" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="inlineStr">
+      <c r="A161" s="28" t="inlineStr">
         <is>
           <t>四、账面价值</t>
         </is>
       </c>
-      <c r="B161" s="13" t="inlineStr"/>
-      <c r="C161" s="13" t="inlineStr"/>
-      <c r="D161" s="13" t="inlineStr"/>
-      <c r="E161" s="13" t="inlineStr"/>
-      <c r="F161" s="15" t="inlineStr"/>
+      <c r="B161" s="18" t="inlineStr"/>
+      <c r="C161" s="18" t="inlineStr"/>
+      <c r="D161" s="18" t="inlineStr"/>
+      <c r="E161" s="18" t="inlineStr"/>
+      <c r="F161" s="19" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -2801,24 +2815,24 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="inlineStr">
+      <c r="A163" s="29" t="inlineStr">
         <is>
           <t>2、期初账面价值</t>
         </is>
       </c>
-      <c r="B163" s="9" t="n">
+      <c r="B163" s="30" t="n">
         <v>35172985.52</v>
       </c>
-      <c r="C163" s="9" t="n">
+      <c r="C163" s="30" t="n">
         <v>377363.88</v>
       </c>
-      <c r="D163" s="9" t="n">
+      <c r="D163" s="30" t="n">
         <v>179685.57</v>
       </c>
-      <c r="E163" s="9" t="n">
+      <c r="E163" s="30" t="n">
         <v>262972.49</v>
       </c>
-      <c r="F163" s="10" t="n">
+      <c r="F163" s="31" t="n">
         <v>35993007.46</v>
       </c>
     </row>
@@ -2844,17 +2858,17 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" s="32" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B168" s="33" t="inlineStr">
         <is>
           <t>房屋及建筑物</t>
         </is>
       </c>
-      <c r="C168" s="4" t="inlineStr">
+      <c r="C168" s="34" t="inlineStr">
         <is>
           <t>合  计</t>
         </is>
@@ -2866,8 +2880,8 @@
           <t>一、账面原值</t>
         </is>
       </c>
-      <c r="B169" s="13" t="inlineStr"/>
-      <c r="C169" s="15" t="inlineStr"/>
+      <c r="B169" s="18" t="inlineStr"/>
+      <c r="C169" s="19" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -2888,8 +2902,8 @@
           <t>2、本期增加金额</t>
         </is>
       </c>
-      <c r="B171" s="13" t="inlineStr"/>
-      <c r="C171" s="15" t="inlineStr"/>
+      <c r="B171" s="18" t="inlineStr"/>
+      <c r="C171" s="19" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -2897,8 +2911,8 @@
           <t>(1)租入</t>
         </is>
       </c>
-      <c r="B172" s="13" t="inlineStr"/>
-      <c r="C172" s="15" t="inlineStr"/>
+      <c r="B172" s="18" t="inlineStr"/>
+      <c r="C172" s="19" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -2906,8 +2920,8 @@
           <t>3、本期减少金额</t>
         </is>
       </c>
-      <c r="B173" s="13" t="inlineStr"/>
-      <c r="C173" s="15" t="inlineStr"/>
+      <c r="B173" s="18" t="inlineStr"/>
+      <c r="C173" s="19" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -2915,8 +2929,8 @@
           <t>(1)退租</t>
         </is>
       </c>
-      <c r="B174" s="13" t="inlineStr"/>
-      <c r="C174" s="15" t="inlineStr"/>
+      <c r="B174" s="18" t="inlineStr"/>
+      <c r="C174" s="19" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -2937,8 +2951,8 @@
           <t>二、累计折旧</t>
         </is>
       </c>
-      <c r="B176" s="13" t="inlineStr"/>
-      <c r="C176" s="15" t="inlineStr"/>
+      <c r="B176" s="18" t="inlineStr"/>
+      <c r="C176" s="19" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -2985,8 +2999,8 @@
           <t>3、本期减少金额</t>
         </is>
       </c>
-      <c r="B180" s="13" t="inlineStr"/>
-      <c r="C180" s="15" t="inlineStr"/>
+      <c r="B180" s="18" t="inlineStr"/>
+      <c r="C180" s="19" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -2994,8 +3008,8 @@
           <t>(1)退租</t>
         </is>
       </c>
-      <c r="B181" s="13" t="inlineStr"/>
-      <c r="C181" s="15" t="inlineStr"/>
+      <c r="B181" s="18" t="inlineStr"/>
+      <c r="C181" s="19" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -3016,8 +3030,8 @@
           <t>三、减值准备</t>
         </is>
       </c>
-      <c r="B183" s="13" t="inlineStr"/>
-      <c r="C183" s="15" t="inlineStr"/>
+      <c r="B183" s="18" t="inlineStr"/>
+      <c r="C183" s="19" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -3025,8 +3039,8 @@
           <t>1、期初余额</t>
         </is>
       </c>
-      <c r="B184" s="13" t="inlineStr"/>
-      <c r="C184" s="15" t="inlineStr"/>
+      <c r="B184" s="18" t="inlineStr"/>
+      <c r="C184" s="19" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -3034,8 +3048,8 @@
           <t>2、本期增加金额</t>
         </is>
       </c>
-      <c r="B185" s="13" t="inlineStr"/>
-      <c r="C185" s="15" t="inlineStr"/>
+      <c r="B185" s="18" t="inlineStr"/>
+      <c r="C185" s="19" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -3043,8 +3057,8 @@
           <t>(1)计提</t>
         </is>
       </c>
-      <c r="B186" s="13" t="inlineStr"/>
-      <c r="C186" s="15" t="inlineStr"/>
+      <c r="B186" s="18" t="inlineStr"/>
+      <c r="C186" s="19" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -3052,8 +3066,8 @@
           <t>3、本期减少金额</t>
         </is>
       </c>
-      <c r="B187" s="13" t="inlineStr"/>
-      <c r="C187" s="15" t="inlineStr"/>
+      <c r="B187" s="18" t="inlineStr"/>
+      <c r="C187" s="19" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -3061,8 +3075,8 @@
           <t>(1)处置</t>
         </is>
       </c>
-      <c r="B188" s="13" t="inlineStr"/>
-      <c r="C188" s="15" t="inlineStr"/>
+      <c r="B188" s="18" t="inlineStr"/>
+      <c r="C188" s="19" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -3070,8 +3084,8 @@
           <t>4、期末余额</t>
         </is>
       </c>
-      <c r="B189" s="13" t="inlineStr"/>
-      <c r="C189" s="15" t="inlineStr"/>
+      <c r="B189" s="18" t="inlineStr"/>
+      <c r="C189" s="19" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -3079,8 +3093,8 @@
           <t>四、账面价值</t>
         </is>
       </c>
-      <c r="B190" s="13" t="inlineStr"/>
-      <c r="C190" s="15" t="inlineStr"/>
+      <c r="B190" s="18" t="inlineStr"/>
+      <c r="C190" s="19" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -3096,15 +3110,15 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="8" t="inlineStr">
+      <c r="A192" s="29" t="inlineStr">
         <is>
           <t>2、期初账面价值</t>
         </is>
       </c>
-      <c r="B192" s="9" t="n">
+      <c r="B192" s="30" t="n">
         <v>1266749.53</v>
       </c>
-      <c r="C192" s="10" t="n">
+      <c r="C192" s="31" t="n">
         <v>1266749.53</v>
       </c>
     </row>
@@ -3116,17 +3130,17 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+      <c r="A195" s="32" t="inlineStr">
         <is>
           <t>项    目</t>
         </is>
       </c>
-      <c r="B195" s="3" t="inlineStr">
+      <c r="B195" s="33" t="inlineStr">
         <is>
           <t>软件</t>
         </is>
       </c>
-      <c r="C195" s="4" t="inlineStr">
+      <c r="C195" s="34" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
@@ -3138,8 +3152,8 @@
           <t>一、账面原值</t>
         </is>
       </c>
-      <c r="B196" s="13" t="inlineStr"/>
-      <c r="C196" s="15" t="inlineStr"/>
+      <c r="B196" s="18" t="inlineStr"/>
+      <c r="C196" s="19" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -3160,8 +3174,8 @@
           <t>2.本期增加金额</t>
         </is>
       </c>
-      <c r="B198" s="13" t="inlineStr"/>
-      <c r="C198" s="15" t="inlineStr"/>
+      <c r="B198" s="18" t="inlineStr"/>
+      <c r="C198" s="19" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
@@ -3169,8 +3183,8 @@
           <t>(1)购置</t>
         </is>
       </c>
-      <c r="B199" s="13" t="inlineStr"/>
-      <c r="C199" s="15" t="inlineStr"/>
+      <c r="B199" s="18" t="inlineStr"/>
+      <c r="C199" s="19" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -3178,8 +3192,8 @@
           <t>(2)内部研发</t>
         </is>
       </c>
-      <c r="B200" s="13" t="inlineStr"/>
-      <c r="C200" s="15" t="inlineStr"/>
+      <c r="B200" s="18" t="inlineStr"/>
+      <c r="C200" s="19" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
@@ -3187,8 +3201,8 @@
           <t>(3)企业合并增加</t>
         </is>
       </c>
-      <c r="B201" s="13" t="inlineStr"/>
-      <c r="C201" s="15" t="inlineStr"/>
+      <c r="B201" s="18" t="inlineStr"/>
+      <c r="C201" s="19" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -3196,8 +3210,8 @@
           <t>3.本期减少金额</t>
         </is>
       </c>
-      <c r="B202" s="13" t="inlineStr"/>
-      <c r="C202" s="15" t="inlineStr"/>
+      <c r="B202" s="18" t="inlineStr"/>
+      <c r="C202" s="19" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
@@ -3205,8 +3219,8 @@
           <t>(1)处置</t>
         </is>
       </c>
-      <c r="B203" s="13" t="inlineStr"/>
-      <c r="C203" s="15" t="inlineStr"/>
+      <c r="B203" s="18" t="inlineStr"/>
+      <c r="C203" s="19" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -3227,8 +3241,8 @@
           <t>二、累计摊销</t>
         </is>
       </c>
-      <c r="B205" s="13" t="inlineStr"/>
-      <c r="C205" s="15" t="inlineStr"/>
+      <c r="B205" s="18" t="inlineStr"/>
+      <c r="C205" s="19" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -3275,8 +3289,8 @@
           <t>3.本期减少金额</t>
         </is>
       </c>
-      <c r="B209" s="13" t="inlineStr"/>
-      <c r="C209" s="15" t="inlineStr"/>
+      <c r="B209" s="18" t="inlineStr"/>
+      <c r="C209" s="19" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -3284,8 +3298,8 @@
           <t>(1)处置</t>
         </is>
       </c>
-      <c r="B210" s="13" t="inlineStr"/>
-      <c r="C210" s="15" t="inlineStr"/>
+      <c r="B210" s="18" t="inlineStr"/>
+      <c r="C210" s="19" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
@@ -3306,8 +3320,8 @@
           <t>三、减值准备</t>
         </is>
       </c>
-      <c r="B212" s="13" t="inlineStr"/>
-      <c r="C212" s="15" t="inlineStr"/>
+      <c r="B212" s="18" t="inlineStr"/>
+      <c r="C212" s="19" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -3315,8 +3329,8 @@
           <t>1.期初余额</t>
         </is>
       </c>
-      <c r="B213" s="13" t="inlineStr"/>
-      <c r="C213" s="15" t="inlineStr"/>
+      <c r="B213" s="18" t="inlineStr"/>
+      <c r="C213" s="19" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -3324,8 +3338,8 @@
           <t>2.本期增加金额</t>
         </is>
       </c>
-      <c r="B214" s="13" t="inlineStr"/>
-      <c r="C214" s="15" t="inlineStr"/>
+      <c r="B214" s="18" t="inlineStr"/>
+      <c r="C214" s="19" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -3333,8 +3347,8 @@
           <t>（1）计提</t>
         </is>
       </c>
-      <c r="B215" s="13" t="inlineStr"/>
-      <c r="C215" s="15" t="inlineStr"/>
+      <c r="B215" s="18" t="inlineStr"/>
+      <c r="C215" s="19" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -3342,8 +3356,8 @@
           <t>3.本期减少金额</t>
         </is>
       </c>
-      <c r="B216" s="13" t="inlineStr"/>
-      <c r="C216" s="15" t="inlineStr"/>
+      <c r="B216" s="18" t="inlineStr"/>
+      <c r="C216" s="19" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -3351,8 +3365,8 @@
           <t>(1)处置</t>
         </is>
       </c>
-      <c r="B217" s="13" t="inlineStr"/>
-      <c r="C217" s="15" t="inlineStr"/>
+      <c r="B217" s="18" t="inlineStr"/>
+      <c r="C217" s="19" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -3360,8 +3374,8 @@
           <t>4.期末余额</t>
         </is>
       </c>
-      <c r="B218" s="13" t="inlineStr"/>
-      <c r="C218" s="15" t="inlineStr"/>
+      <c r="B218" s="18" t="inlineStr"/>
+      <c r="C218" s="19" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
@@ -3369,8 +3383,8 @@
           <t>四、账面价值</t>
         </is>
       </c>
-      <c r="B219" s="13" t="inlineStr"/>
-      <c r="C219" s="15" t="inlineStr"/>
+      <c r="B219" s="18" t="inlineStr"/>
+      <c r="C219" s="19" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -3386,15 +3400,15 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="8" t="inlineStr">
+      <c r="A221" s="29" t="inlineStr">
         <is>
           <t>2.期初账面价值</t>
         </is>
       </c>
-      <c r="B221" s="9" t="n">
+      <c r="B221" s="30" t="n">
         <v>945480.8199999999</v>
       </c>
-      <c r="C221" s="10" t="n">
+      <c r="C221" s="31" t="n">
         <v>945480.8199999999</v>
       </c>
     </row>
@@ -3416,7 +3430,7 @@
           <t>期末余额</t>
         </is>
       </c>
-      <c r="C224" s="22" t="n"/>
+      <c r="C224" s="25" t="n"/>
       <c r="D224" s="4" t="inlineStr">
         <is>
           <t>期初余额</t>
@@ -3448,15 +3462,15 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="inlineStr">
+      <c r="A226" s="28" t="inlineStr">
         <is>
           <t>递延所得税资产</t>
         </is>
       </c>
-      <c r="B226" s="13" t="inlineStr"/>
-      <c r="C226" s="13" t="inlineStr"/>
-      <c r="D226" s="13" t="inlineStr"/>
-      <c r="E226" s="15" t="inlineStr"/>
+      <c r="B226" s="18" t="inlineStr"/>
+      <c r="C226" s="18" t="inlineStr"/>
+      <c r="D226" s="18" t="inlineStr"/>
+      <c r="E226" s="19" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
@@ -3516,34 +3530,34 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="inlineStr">
+      <c r="A230" s="28" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="B230" s="6" t="n">
+      <c r="B230" s="35" t="n">
         <v>21756387.76</v>
       </c>
-      <c r="C230" s="6" t="n">
+      <c r="C230" s="35" t="n">
         <v>145084148.53</v>
       </c>
-      <c r="D230" s="6" t="n">
+      <c r="D230" s="35" t="n">
         <v>18657101.59</v>
       </c>
-      <c r="E230" s="7" t="n">
+      <c r="E230" s="36" t="n">
         <v>124380677.25</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="inlineStr">
+      <c r="A231" s="28" t="inlineStr">
         <is>
           <t>递延所得税负债</t>
         </is>
       </c>
-      <c r="B231" s="13" t="inlineStr"/>
-      <c r="C231" s="13" t="inlineStr"/>
-      <c r="D231" s="13" t="inlineStr"/>
-      <c r="E231" s="15" t="inlineStr"/>
+      <c r="B231" s="18" t="inlineStr"/>
+      <c r="C231" s="18" t="inlineStr"/>
+      <c r="D231" s="18" t="inlineStr"/>
+      <c r="E231" s="19" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -3613,10 +3627,10 @@
           <t>信用借款</t>
         </is>
       </c>
-      <c r="B237" s="20" t="n">
+      <c r="B237" s="22" t="n">
         <v>7008750</v>
       </c>
-      <c r="C237" s="23" t="n">
+      <c r="C237" s="26" t="n">
         <v>10012500</v>
       </c>
     </row>
@@ -3626,10 +3640,10 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B238" s="18" t="n">
+      <c r="B238" s="20" t="n">
         <v>7008750</v>
       </c>
-      <c r="C238" s="24" t="n">
+      <c r="C238" s="27" t="n">
         <v>10012500</v>
       </c>
     </row>
@@ -3670,7 +3684,7 @@
           <t>1年以内</t>
         </is>
       </c>
-      <c r="B243" s="20" t="n">
+      <c r="B243" s="22" t="n">
         <v>223200</v>
       </c>
       <c r="C243" s="7" t="n">
@@ -3686,7 +3700,7 @@
       <c r="B244" s="6" t="n">
         <v>4391.27</v>
       </c>
-      <c r="C244" s="15" t="inlineStr"/>
+      <c r="C244" s="19" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="8" t="inlineStr">
@@ -3709,27 +3723,27 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+      <c r="A248" s="32" t="inlineStr">
         <is>
           <t>单位名称</t>
         </is>
       </c>
-      <c r="B248" s="3" t="inlineStr">
+      <c r="B248" s="33" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C248" s="3" t="inlineStr">
+      <c r="C248" s="33" t="inlineStr">
         <is>
           <t>账龄</t>
         </is>
       </c>
-      <c r="D248" s="3" t="inlineStr">
+      <c r="D248" s="33" t="inlineStr">
         <is>
           <t>占应付账款合计金额的比例（%）</t>
         </is>
       </c>
-      <c r="E248" s="4" t="inlineStr">
+      <c r="E248" s="34" t="inlineStr">
         <is>
           <t>款项性质</t>
         </is>
@@ -3741,10 +3755,10 @@
           <t>常州皓鸣信息科技有限公司</t>
         </is>
       </c>
-      <c r="B249" s="20" t="n">
+      <c r="B249" s="22" t="n">
         <v>223200</v>
       </c>
-      <c r="C249" s="13" t="inlineStr">
+      <c r="C249" s="18" t="inlineStr">
         <is>
           <t>1年以内</t>
         </is>
@@ -3752,7 +3766,7 @@
       <c r="D249" s="6" t="n">
         <v>98.06999999999999</v>
       </c>
-      <c r="E249" s="15" t="inlineStr">
+      <c r="E249" s="19" t="inlineStr">
         <is>
           <t>技术服务费</t>
         </is>
@@ -3767,7 +3781,7 @@
       <c r="B250" s="6" t="n">
         <v>4391.27</v>
       </c>
-      <c r="C250" s="13" t="inlineStr">
+      <c r="C250" s="18" t="inlineStr">
         <is>
           <t>1-2年</t>
         </is>
@@ -3775,7 +3789,7 @@
       <c r="D250" s="6" t="n">
         <v>1.93</v>
       </c>
-      <c r="E250" s="15" t="inlineStr">
+      <c r="E250" s="19" t="inlineStr">
         <is>
           <t>物业管理费</t>
         </is>
@@ -3790,11 +3804,11 @@
       <c r="B251" s="9" t="n">
         <v>227591.27</v>
       </c>
-      <c r="C251" s="19" t="inlineStr"/>
-      <c r="D251" s="18" t="n">
+      <c r="C251" s="21" t="inlineStr"/>
+      <c r="D251" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="E251" s="21" t="inlineStr"/>
+      <c r="E251" s="24" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3849,7 +3863,7 @@
       <c r="B257" s="6" t="n">
         <v>2999.46</v>
       </c>
-      <c r="C257" s="15" t="inlineStr"/>
+      <c r="C257" s="19" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="8" t="inlineStr">
@@ -3930,14 +3944,14 @@
           <t>离职后福利-设定提存计划</t>
         </is>
       </c>
-      <c r="B264" s="13" t="inlineStr"/>
+      <c r="B264" s="18" t="inlineStr"/>
       <c r="C264" s="6" t="n">
         <v>446986.09</v>
       </c>
       <c r="D264" s="6" t="n">
         <v>446986.09</v>
       </c>
-      <c r="E264" s="15" t="inlineStr"/>
+      <c r="E264" s="19" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="8" t="inlineStr">
@@ -3945,16 +3959,16 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B265" s="9" t="n">
+      <c r="B265" s="30" t="n">
         <v>3777974.16</v>
       </c>
-      <c r="C265" s="9" t="n">
+      <c r="C265" s="30" t="n">
         <v>12252734.34</v>
       </c>
-      <c r="D265" s="9" t="n">
+      <c r="D265" s="30" t="n">
         <v>14923680.52</v>
       </c>
-      <c r="E265" s="10" t="n">
+      <c r="E265" s="31" t="n">
         <v>1107027.98</v>
       </c>
     </row>
@@ -4017,14 +4031,14 @@
           <t>(2)职工福利费</t>
         </is>
       </c>
-      <c r="B270" s="13" t="inlineStr"/>
-      <c r="C270" s="20" t="n">
+      <c r="B270" s="18" t="inlineStr"/>
+      <c r="C270" s="22" t="n">
         <v>1804</v>
       </c>
-      <c r="D270" s="20" t="n">
+      <c r="D270" s="22" t="n">
         <v>1804</v>
       </c>
-      <c r="E270" s="15" t="inlineStr"/>
+      <c r="E270" s="19" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
@@ -4032,14 +4046,14 @@
           <t>(3)社会保险费</t>
         </is>
       </c>
-      <c r="B271" s="13" t="inlineStr"/>
+      <c r="B271" s="18" t="inlineStr"/>
       <c r="C271" s="6" t="n">
         <v>205199.1</v>
       </c>
       <c r="D271" s="6" t="n">
         <v>205199.1</v>
       </c>
-      <c r="E271" s="15" t="inlineStr"/>
+      <c r="E271" s="19" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
@@ -4047,14 +4061,14 @@
           <t>其中：医疗保险费</t>
         </is>
       </c>
-      <c r="B272" s="13" t="inlineStr"/>
+      <c r="B272" s="18" t="inlineStr"/>
       <c r="C272" s="6" t="n">
         <v>189727.45</v>
       </c>
       <c r="D272" s="6" t="n">
         <v>189727.45</v>
       </c>
-      <c r="E272" s="15" t="inlineStr"/>
+      <c r="E272" s="19" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
@@ -4062,14 +4076,14 @@
           <t>工伤保险费</t>
         </is>
       </c>
-      <c r="B273" s="13" t="inlineStr"/>
+      <c r="B273" s="18" t="inlineStr"/>
       <c r="C273" s="6" t="n">
         <v>3990.18</v>
       </c>
       <c r="D273" s="6" t="n">
         <v>3990.18</v>
       </c>
-      <c r="E273" s="15" t="inlineStr"/>
+      <c r="E273" s="19" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
@@ -4077,14 +4091,14 @@
           <t>生育保险费</t>
         </is>
       </c>
-      <c r="B274" s="13" t="inlineStr"/>
+      <c r="B274" s="18" t="inlineStr"/>
       <c r="C274" s="6" t="n">
         <v>11481.47</v>
       </c>
       <c r="D274" s="6" t="n">
         <v>11481.47</v>
       </c>
-      <c r="E274" s="15" t="inlineStr"/>
+      <c r="E274" s="19" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
@@ -4092,14 +4106,14 @@
           <t>(4)住房公积金</t>
         </is>
       </c>
-      <c r="B275" s="13" t="inlineStr"/>
+      <c r="B275" s="18" t="inlineStr"/>
       <c r="C275" s="6" t="n">
         <v>743495.5</v>
       </c>
       <c r="D275" s="6" t="n">
         <v>743495.5</v>
       </c>
-      <c r="E275" s="15" t="inlineStr"/>
+      <c r="E275" s="19" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
@@ -4107,10 +4121,10 @@
           <t>(5)工会经费和职工教育经费</t>
         </is>
       </c>
-      <c r="B276" s="13" t="inlineStr"/>
-      <c r="C276" s="13" t="inlineStr"/>
-      <c r="D276" s="13" t="inlineStr"/>
-      <c r="E276" s="15" t="inlineStr"/>
+      <c r="B276" s="18" t="inlineStr"/>
+      <c r="C276" s="18" t="inlineStr"/>
+      <c r="D276" s="18" t="inlineStr"/>
+      <c r="E276" s="19" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="8" t="inlineStr">
@@ -4118,16 +4132,16 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B277" s="9" t="n">
+      <c r="B277" s="30" t="n">
         <v>3777974.16</v>
       </c>
-      <c r="C277" s="9" t="n">
+      <c r="C277" s="30" t="n">
         <v>11805748.25</v>
       </c>
-      <c r="D277" s="9" t="n">
+      <c r="D277" s="30" t="n">
         <v>14476694.43</v>
       </c>
-      <c r="E277" s="10" t="n">
+      <c r="E277" s="31" t="n">
         <v>1107027.98</v>
       </c>
     </row>
@@ -4171,14 +4185,14 @@
           <t>基本养老保险</t>
         </is>
       </c>
-      <c r="B281" s="13" t="inlineStr"/>
+      <c r="B281" s="18" t="inlineStr"/>
       <c r="C281" s="6" t="n">
         <v>433192.36</v>
       </c>
       <c r="D281" s="6" t="n">
         <v>433192.36</v>
       </c>
-      <c r="E281" s="15" t="inlineStr"/>
+      <c r="E281" s="19" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
@@ -4186,14 +4200,14 @@
           <t>失业保险费</t>
         </is>
       </c>
-      <c r="B282" s="13" t="inlineStr"/>
+      <c r="B282" s="18" t="inlineStr"/>
       <c r="C282" s="6" t="n">
         <v>13793.73</v>
       </c>
       <c r="D282" s="6" t="n">
         <v>13793.73</v>
       </c>
-      <c r="E282" s="15" t="inlineStr"/>
+      <c r="E282" s="19" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="8" t="inlineStr">
@@ -4201,14 +4215,14 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B283" s="19" t="inlineStr"/>
-      <c r="C283" s="9" t="n">
+      <c r="B283" s="21" t="inlineStr"/>
+      <c r="C283" s="30" t="n">
         <v>446986.09</v>
       </c>
-      <c r="D283" s="9" t="n">
+      <c r="D283" s="30" t="n">
         <v>446986.09</v>
       </c>
-      <c r="E283" s="21" t="inlineStr"/>
+      <c r="E283" s="24" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
@@ -4321,7 +4335,7 @@
       <c r="B293" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="C293" s="15" t="inlineStr"/>
+      <c r="C293" s="19" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="8" t="inlineStr">
@@ -4373,8 +4387,8 @@
           <t>应付利息</t>
         </is>
       </c>
-      <c r="B299" s="13" t="inlineStr"/>
-      <c r="C299" s="15" t="inlineStr"/>
+      <c r="B299" s="18" t="inlineStr"/>
+      <c r="C299" s="19" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
@@ -4382,8 +4396,8 @@
           <t>应付股利</t>
         </is>
       </c>
-      <c r="B300" s="13" t="inlineStr"/>
-      <c r="C300" s="15" t="inlineStr"/>
+      <c r="B300" s="18" t="inlineStr"/>
+      <c r="C300" s="19" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
@@ -4467,7 +4481,7 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B308" s="13" t="inlineStr"/>
+      <c r="B308" s="18" t="inlineStr"/>
       <c r="C308" s="7" t="n">
         <v>100.72</v>
       </c>
@@ -4493,27 +4507,27 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="inlineStr">
+      <c r="A312" s="32" t="inlineStr">
         <is>
           <t>单位名称</t>
         </is>
       </c>
-      <c r="B312" s="3" t="inlineStr">
+      <c r="B312" s="33" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C312" s="3" t="inlineStr">
+      <c r="C312" s="33" t="inlineStr">
         <is>
           <t>账龄</t>
         </is>
       </c>
-      <c r="D312" s="3" t="inlineStr">
+      <c r="D312" s="33" t="inlineStr">
         <is>
           <t>占其他应付款合计金额的比例（%）</t>
         </is>
       </c>
-      <c r="E312" s="4" t="inlineStr">
+      <c r="E312" s="34" t="inlineStr">
         <is>
           <t>款项性质</t>
         </is>
@@ -4528,7 +4542,7 @@
       <c r="B313" s="6" t="n">
         <v>45831569.41</v>
       </c>
-      <c r="C313" s="13" t="inlineStr">
+      <c r="C313" s="18" t="inlineStr">
         <is>
           <t>1年以内</t>
         </is>
@@ -4536,7 +4550,7 @@
       <c r="D313" s="6" t="n">
         <v>64.33</v>
       </c>
-      <c r="E313" s="15" t="inlineStr">
+      <c r="E313" s="19" t="inlineStr">
         <is>
           <t>关联方往来款</t>
         </is>
@@ -4551,11 +4565,11 @@
       <c r="B314" s="9" t="n">
         <v>45831569.41</v>
       </c>
-      <c r="C314" s="19" t="inlineStr"/>
+      <c r="C314" s="23" t="inlineStr"/>
       <c r="D314" s="9" t="n">
         <v>64.33</v>
       </c>
-      <c r="E314" s="21" t="inlineStr"/>
+      <c r="E314" s="24" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -4644,7 +4658,7 @@
           <t>房屋租赁</t>
         </is>
       </c>
-      <c r="B324" s="13" t="inlineStr"/>
+      <c r="B324" s="18" t="inlineStr"/>
       <c r="C324" s="7" t="n">
         <v>260119.77</v>
       </c>
@@ -4655,7 +4669,7 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B325" s="19" t="inlineStr"/>
+      <c r="B325" s="21" t="inlineStr"/>
       <c r="C325" s="10" t="n">
         <v>260119.77</v>
       </c>
@@ -4706,7 +4720,7 @@
       <c r="B330" s="9" t="n">
         <v>206224.83</v>
       </c>
-      <c r="C330" s="10" t="n">
+      <c r="C330" s="31" t="n">
         <v>247788.3</v>
       </c>
     </row>
@@ -4728,7 +4742,7 @@
           <t>期初余额</t>
         </is>
       </c>
-      <c r="C333" s="22" t="n"/>
+      <c r="C333" s="25" t="n"/>
       <c r="D333" s="3" t="inlineStr">
         <is>
           <t>本期增加</t>
@@ -4758,8 +4772,8 @@
           <t>比例%</t>
         </is>
       </c>
-      <c r="D334" s="25" t="n"/>
-      <c r="E334" s="25" t="n"/>
+      <c r="D334" s="37" t="n"/>
+      <c r="E334" s="37" t="n"/>
       <c r="F334" s="13" t="inlineStr">
         <is>
           <t>金额</t>
@@ -4777,18 +4791,18 @@
           <t>深圳市一方保成科技有限公司</t>
         </is>
       </c>
-      <c r="B335" s="20" t="n">
+      <c r="B335" s="22" t="n">
         <v>5000000</v>
       </c>
-      <c r="C335" s="20" t="n">
+      <c r="C335" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="D335" s="13" t="inlineStr"/>
-      <c r="E335" s="13" t="inlineStr"/>
-      <c r="F335" s="20" t="n">
+      <c r="D335" s="18" t="inlineStr"/>
+      <c r="E335" s="18" t="inlineStr"/>
+      <c r="F335" s="22" t="n">
         <v>5000000</v>
       </c>
-      <c r="G335" s="23" t="n">
+      <c r="G335" s="26" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4798,18 +4812,18 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B336" s="18" t="n">
+      <c r="B336" s="20" t="n">
         <v>5000000</v>
       </c>
-      <c r="C336" s="18" t="n">
+      <c r="C336" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D336" s="19" t="inlineStr"/>
-      <c r="E336" s="19" t="inlineStr"/>
-      <c r="F336" s="18" t="n">
+      <c r="D336" s="21" t="inlineStr"/>
+      <c r="E336" s="21" t="inlineStr"/>
+      <c r="F336" s="20" t="n">
         <v>5000000</v>
       </c>
-      <c r="G336" s="24" t="n">
+      <c r="G336" s="27" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4856,8 +4870,8 @@
       <c r="B340" s="6" t="n">
         <v>3547783.93</v>
       </c>
-      <c r="C340" s="13" t="inlineStr"/>
-      <c r="D340" s="13" t="inlineStr"/>
+      <c r="C340" s="18" t="inlineStr"/>
+      <c r="D340" s="18" t="inlineStr"/>
       <c r="E340" s="7" t="n">
         <v>3547783.93</v>
       </c>
@@ -4871,8 +4885,8 @@
       <c r="B341" s="9" t="n">
         <v>3547783.93</v>
       </c>
-      <c r="C341" s="19" t="inlineStr"/>
-      <c r="D341" s="19" t="inlineStr"/>
+      <c r="C341" s="21" t="inlineStr"/>
+      <c r="D341" s="21" t="inlineStr"/>
       <c r="E341" s="10" t="n">
         <v>3547783.93</v>
       </c>
@@ -4920,8 +4934,8 @@
       <c r="B345" s="6" t="n">
         <v>5634537.09</v>
       </c>
-      <c r="C345" s="13" t="inlineStr"/>
-      <c r="D345" s="13" t="inlineStr"/>
+      <c r="C345" s="18" t="inlineStr"/>
+      <c r="D345" s="18" t="inlineStr"/>
       <c r="E345" s="7" t="n">
         <v>5634537.09</v>
       </c>
@@ -4935,8 +4949,8 @@
       <c r="B346" s="9" t="n">
         <v>5634537.09</v>
       </c>
-      <c r="C346" s="19" t="inlineStr"/>
-      <c r="D346" s="19" t="inlineStr"/>
+      <c r="C346" s="21" t="inlineStr"/>
+      <c r="D346" s="21" t="inlineStr"/>
       <c r="E346" s="10" t="n">
         <v>5634537.09</v>
       </c>
@@ -4974,7 +4988,7 @@
       <c r="B350" s="6" t="n">
         <v>-3669458.07</v>
       </c>
-      <c r="C350" s="23" t="n">
+      <c r="C350" s="26" t="n">
         <v>17377317</v>
       </c>
     </row>
@@ -4984,8 +4998,8 @@
           <t>加：期初未分配利润调整额</t>
         </is>
       </c>
-      <c r="B351" s="13" t="inlineStr"/>
-      <c r="C351" s="15" t="inlineStr"/>
+      <c r="B351" s="18" t="inlineStr"/>
+      <c r="C351" s="19" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="5" t="inlineStr">
@@ -4996,7 +5010,7 @@
       <c r="B352" s="6" t="n">
         <v>-3669458.07</v>
       </c>
-      <c r="C352" s="23" t="n">
+      <c r="C352" s="26" t="n">
         <v>17377317</v>
       </c>
     </row>
@@ -5032,8 +5046,8 @@
           <t>本期减少额</t>
         </is>
       </c>
-      <c r="B355" s="13" t="inlineStr"/>
-      <c r="C355" s="15" t="inlineStr"/>
+      <c r="B355" s="18" t="inlineStr"/>
+      <c r="C355" s="19" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="5" t="inlineStr">
@@ -5041,8 +5055,8 @@
           <t>其中：本期提取法定盈余公积额</t>
         </is>
       </c>
-      <c r="B356" s="13" t="inlineStr"/>
-      <c r="C356" s="15" t="inlineStr"/>
+      <c r="B356" s="18" t="inlineStr"/>
+      <c r="C356" s="19" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="5" t="inlineStr">
@@ -5050,8 +5064,8 @@
           <t>应付股利</t>
         </is>
       </c>
-      <c r="B357" s="13" t="inlineStr"/>
-      <c r="C357" s="15" t="inlineStr"/>
+      <c r="B357" s="18" t="inlineStr"/>
+      <c r="C357" s="19" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="5" t="inlineStr">
@@ -5059,8 +5073,8 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B358" s="13" t="inlineStr"/>
-      <c r="C358" s="15" t="inlineStr"/>
+      <c r="B358" s="18" t="inlineStr"/>
+      <c r="C358" s="19" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="8" t="inlineStr">
@@ -5068,10 +5082,10 @@
           <t>本期期末余额</t>
         </is>
       </c>
-      <c r="B359" s="9" t="n">
+      <c r="B359" s="30" t="n">
         <v>-11837137.85</v>
       </c>
-      <c r="C359" s="10" t="n">
+      <c r="C359" s="31" t="n">
         <v>-3669458.07</v>
       </c>
     </row>
@@ -5100,7 +5114,7 @@
           <t>本期发生额</t>
         </is>
       </c>
-      <c r="C363" s="22" t="n"/>
+      <c r="C363" s="25" t="n"/>
       <c r="D363" s="4" t="inlineStr">
         <is>
           <t>上期发生额</t>
@@ -5137,14 +5151,14 @@
           <t>主营业务</t>
         </is>
       </c>
-      <c r="B365" s="20" t="n">
+      <c r="B365" s="22" t="n">
         <v>19720767</v>
       </c>
-      <c r="C365" s="13" t="inlineStr"/>
+      <c r="C365" s="18" t="inlineStr"/>
       <c r="D365" s="6" t="n">
         <v>24488692.83</v>
       </c>
-      <c r="E365" s="15" t="inlineStr"/>
+      <c r="E365" s="19" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="5" t="inlineStr">
@@ -5152,10 +5166,10 @@
           <t>其他业务</t>
         </is>
       </c>
-      <c r="B366" s="13" t="inlineStr"/>
-      <c r="C366" s="13" t="inlineStr"/>
-      <c r="D366" s="13" t="inlineStr"/>
-      <c r="E366" s="15" t="inlineStr"/>
+      <c r="B366" s="18" t="inlineStr"/>
+      <c r="C366" s="18" t="inlineStr"/>
+      <c r="D366" s="18" t="inlineStr"/>
+      <c r="E366" s="19" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="8" t="inlineStr">
@@ -5163,14 +5177,14 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B367" s="18" t="n">
+      <c r="B367" s="20" t="n">
         <v>19720767</v>
       </c>
-      <c r="C367" s="19" t="inlineStr"/>
+      <c r="C367" s="21" t="inlineStr"/>
       <c r="D367" s="9" t="n">
         <v>24488692.83</v>
       </c>
-      <c r="E367" s="21" t="inlineStr"/>
+      <c r="E367" s="24" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -5228,7 +5242,7 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B373" s="18" t="n">
+      <c r="B373" s="20" t="n">
         <v>19720767</v>
       </c>
       <c r="C373" s="10" t="n">
@@ -5343,8 +5357,8 @@
           <t>车船税</t>
         </is>
       </c>
-      <c r="B383" s="13" t="inlineStr"/>
-      <c r="C383" s="23" t="n">
+      <c r="B383" s="18" t="inlineStr"/>
+      <c r="C383" s="26" t="n">
         <v>360</v>
       </c>
     </row>
@@ -5495,7 +5509,7 @@
           <t>物业管理费</t>
         </is>
       </c>
-      <c r="B396" s="13" t="inlineStr"/>
+      <c r="B396" s="18" t="inlineStr"/>
       <c r="C396" s="7" t="n">
         <v>2312.5</v>
       </c>
@@ -5582,7 +5596,7 @@
           <t>业务招待费</t>
         </is>
       </c>
-      <c r="B404" s="20" t="n">
+      <c r="B404" s="22" t="n">
         <v>799380</v>
       </c>
       <c r="C404" s="7" t="n">
@@ -5660,7 +5674,7 @@
           <t>租赁费</t>
         </is>
       </c>
-      <c r="B410" s="13" t="inlineStr"/>
+      <c r="B410" s="18" t="inlineStr"/>
       <c r="C410" s="7" t="n">
         <v>9433.959999999999</v>
       </c>
@@ -5810,8 +5824,8 @@
           <t>其中：租赁负债的利息费用</t>
         </is>
       </c>
-      <c r="B424" s="13" t="inlineStr"/>
-      <c r="C424" s="15" t="inlineStr"/>
+      <c r="B424" s="18" t="inlineStr"/>
+      <c r="C424" s="19" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="5" t="inlineStr">
@@ -5882,7 +5896,7 @@
           <t>政府补助</t>
         </is>
       </c>
-      <c r="B431" s="20" t="n">
+      <c r="B431" s="22" t="n">
         <v>5200</v>
       </c>
       <c r="C431" s="7" t="n">
@@ -5945,7 +5959,7 @@
           <t>处置未划分为持有待售的非流动资产产生的利得或损失</t>
         </is>
       </c>
-      <c r="B437" s="13" t="inlineStr"/>
+      <c r="B437" s="18" t="inlineStr"/>
       <c r="C437" s="7" t="n">
         <v>-994.9299999999999</v>
       </c>
@@ -5956,7 +5970,7 @@
           <t>其中：固定资产</t>
         </is>
       </c>
-      <c r="B438" s="13" t="inlineStr"/>
+      <c r="B438" s="18" t="inlineStr"/>
       <c r="C438" s="7" t="n">
         <v>-994.9299999999999</v>
       </c>
@@ -5967,8 +5981,8 @@
           <t>使用权资产</t>
         </is>
       </c>
-      <c r="B439" s="13" t="inlineStr"/>
-      <c r="C439" s="15" t="inlineStr"/>
+      <c r="B439" s="18" t="inlineStr"/>
+      <c r="C439" s="19" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="8" t="inlineStr">
@@ -5976,7 +5990,7 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B440" s="19" t="inlineStr"/>
+      <c r="B440" s="21" t="inlineStr"/>
       <c r="C440" s="10" t="n">
         <v>-994.9299999999999</v>
       </c>
@@ -6026,7 +6040,7 @@
       <c r="D444" s="6" t="n">
         <v>26.49</v>
       </c>
-      <c r="E444" s="15" t="n"/>
+      <c r="E444" s="19" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="8" t="inlineStr">
@@ -6043,7 +6057,7 @@
       <c r="D445" s="9" t="n">
         <v>26.49</v>
       </c>
-      <c r="E445" s="21" t="n"/>
+      <c r="E445" s="24" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="1" t="inlineStr">
@@ -6080,11 +6094,11 @@
           <t>税收滞纳金</t>
         </is>
       </c>
-      <c r="B449" s="13" t="inlineStr"/>
+      <c r="B449" s="18" t="inlineStr"/>
       <c r="C449" s="6" t="n">
         <v>15777.52</v>
       </c>
-      <c r="D449" s="15" t="inlineStr"/>
+      <c r="D449" s="19" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="5" t="inlineStr">
@@ -6092,11 +6106,11 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B450" s="13" t="inlineStr"/>
-      <c r="C450" s="20" t="n">
+      <c r="B450" s="18" t="inlineStr"/>
+      <c r="C450" s="22" t="n">
         <v>6800</v>
       </c>
-      <c r="D450" s="15" t="inlineStr"/>
+      <c r="D450" s="19" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="8" t="inlineStr">
@@ -6104,11 +6118,11 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B451" s="19" t="inlineStr"/>
+      <c r="B451" s="21" t="inlineStr"/>
       <c r="C451" s="9" t="n">
         <v>22577.52</v>
       </c>
-      <c r="D451" s="21" t="inlineStr"/>
+      <c r="D451" s="24" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="1" t="inlineStr">
@@ -6140,8 +6154,8 @@
           <t>当期所得税费用</t>
         </is>
       </c>
-      <c r="B455" s="13" t="inlineStr"/>
-      <c r="C455" s="15" t="inlineStr"/>
+      <c r="B455" s="18" t="inlineStr"/>
+      <c r="C455" s="19" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="5" t="inlineStr">
@@ -6199,7 +6213,7 @@
           <t>上期发生额</t>
         </is>
       </c>
-      <c r="D461" s="4" t="n"/>
+      <c r="D461" s="34" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="5" t="inlineStr">
@@ -6213,7 +6227,7 @@
       <c r="C462" s="7" t="n">
         <v>361958460.7</v>
       </c>
-      <c r="D462" s="26" t="n"/>
+      <c r="D462" s="38" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="5" t="inlineStr">
@@ -6221,13 +6235,13 @@
           <t>保证金及押金</t>
         </is>
       </c>
-      <c r="B463" s="20" t="n">
+      <c r="B463" s="22" t="n">
         <v>50000</v>
       </c>
-      <c r="C463" s="23" t="n">
+      <c r="C463" s="26" t="n">
         <v>48300</v>
       </c>
-      <c r="D463" s="26" t="n"/>
+      <c r="D463" s="38" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="5" t="inlineStr">
@@ -6241,7 +6255,7 @@
       <c r="C464" s="7" t="n">
         <v>216698.25</v>
       </c>
-      <c r="D464" s="26" t="n"/>
+      <c r="D464" s="38" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="5" t="inlineStr">
@@ -6255,7 +6269,7 @@
       <c r="C465" s="7" t="n">
         <v>679.08</v>
       </c>
-      <c r="D465" s="26" t="n"/>
+      <c r="D465" s="38" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="5" t="inlineStr">
@@ -6269,7 +6283,7 @@
       <c r="C466" s="7" t="n">
         <v>74112.17</v>
       </c>
-      <c r="D466" s="26" t="n"/>
+      <c r="D466" s="38" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="8" t="inlineStr">
@@ -6283,7 +6297,7 @@
       <c r="C467" s="10" t="n">
         <v>362298250.2</v>
       </c>
-      <c r="D467" s="27" t="n"/>
+      <c r="D467" s="39" t="n"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -6315,7 +6329,7 @@
           <t>往来款代垫款</t>
         </is>
       </c>
-      <c r="B471" s="20" t="n">
+      <c r="B471" s="22" t="n">
         <v>78246991</v>
       </c>
       <c r="C471" s="7" t="n">
@@ -6341,10 +6355,10 @@
           <t>保证金及押金</t>
         </is>
       </c>
-      <c r="B473" s="20" t="n">
+      <c r="B473" s="22" t="n">
         <v>50000</v>
       </c>
-      <c r="C473" s="23" t="n">
+      <c r="C473" s="26" t="n">
         <v>35000</v>
       </c>
     </row>
@@ -6367,7 +6381,7 @@
           <t>营业外支出</t>
         </is>
       </c>
-      <c r="B475" s="13" t="inlineStr"/>
+      <c r="B475" s="18" t="inlineStr"/>
       <c r="C475" s="7" t="n">
         <v>15777.52</v>
       </c>
@@ -6417,13 +6431,13 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="5" t="inlineStr">
+      <c r="A481" s="28" t="inlineStr">
         <is>
           <t>1.将净利润调节为经营活动现金流量：</t>
         </is>
       </c>
-      <c r="B481" s="13" t="inlineStr"/>
-      <c r="C481" s="15" t="inlineStr"/>
+      <c r="B481" s="18" t="inlineStr"/>
+      <c r="C481" s="19" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="5" t="inlineStr">
@@ -6444,8 +6458,8 @@
           <t>加：资产减值准备</t>
         </is>
       </c>
-      <c r="B483" s="13" t="inlineStr"/>
-      <c r="C483" s="15" t="inlineStr"/>
+      <c r="B483" s="18" t="inlineStr"/>
+      <c r="C483" s="19" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="5" t="inlineStr">
@@ -6453,8 +6467,8 @@
           <t>信用减值损失</t>
         </is>
       </c>
-      <c r="B484" s="13" t="inlineStr"/>
-      <c r="C484" s="15" t="inlineStr"/>
+      <c r="B484" s="18" t="inlineStr"/>
+      <c r="C484" s="19" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="5" t="inlineStr">
@@ -6488,8 +6502,8 @@
           <t>长期待摊费用摊销</t>
         </is>
       </c>
-      <c r="B487" s="13" t="inlineStr"/>
-      <c r="C487" s="15" t="inlineStr"/>
+      <c r="B487" s="18" t="inlineStr"/>
+      <c r="C487" s="19" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="5" t="inlineStr">
@@ -6497,8 +6511,8 @@
           <t>低值易耗品摊销</t>
         </is>
       </c>
-      <c r="B488" s="13" t="inlineStr"/>
-      <c r="C488" s="15" t="inlineStr"/>
+      <c r="B488" s="18" t="inlineStr"/>
+      <c r="C488" s="19" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="5" t="inlineStr">
@@ -6506,7 +6520,7 @@
           <t>处置固定资产、无形资产和其他长期资产的损失(收益以“-”号填列)</t>
         </is>
       </c>
-      <c r="B489" s="13" t="inlineStr"/>
+      <c r="B489" s="18" t="inlineStr"/>
       <c r="C489" s="7" t="n">
         <v>994.9299999999999</v>
       </c>
@@ -6517,8 +6531,8 @@
           <t>固定资产报废损失(收益以“-”号填列)</t>
         </is>
       </c>
-      <c r="B490" s="13" t="inlineStr"/>
-      <c r="C490" s="15" t="inlineStr"/>
+      <c r="B490" s="18" t="inlineStr"/>
+      <c r="C490" s="19" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="5" t="inlineStr">
@@ -6526,8 +6540,8 @@
           <t>公允价值变动损失(收益以“-”号填列)</t>
         </is>
       </c>
-      <c r="B491" s="13" t="inlineStr"/>
-      <c r="C491" s="15" t="inlineStr"/>
+      <c r="B491" s="18" t="inlineStr"/>
+      <c r="C491" s="19" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="5" t="inlineStr">
@@ -6548,8 +6562,8 @@
           <t>投资损失(收益以“-”号填列)</t>
         </is>
       </c>
-      <c r="B493" s="13" t="inlineStr"/>
-      <c r="C493" s="15" t="inlineStr"/>
+      <c r="B493" s="18" t="inlineStr"/>
+      <c r="C493" s="19" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="5" t="inlineStr">
@@ -6583,8 +6597,8 @@
           <t>存货的减少(增加以“-”号填列)</t>
         </is>
       </c>
-      <c r="B496" s="13" t="inlineStr"/>
-      <c r="C496" s="15" t="inlineStr"/>
+      <c r="B496" s="18" t="inlineStr"/>
+      <c r="C496" s="19" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="5" t="inlineStr">
@@ -6618,7 +6632,7 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B499" s="13" t="inlineStr"/>
+      <c r="B499" s="18" t="inlineStr"/>
       <c r="C499" s="7" t="n">
         <v>-62058.42</v>
       </c>
@@ -6629,11 +6643,11 @@
           <t>其中：经营性其他流动资产减少(增加以“-”号填列)</t>
         </is>
       </c>
-      <c r="B500" s="13" t="inlineStr"/>
-      <c r="C500" s="15" t="inlineStr"/>
+      <c r="B500" s="18" t="inlineStr"/>
+      <c r="C500" s="19" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="5" t="inlineStr">
+      <c r="A501" s="28" t="inlineStr">
         <is>
           <t>经营活动产生的现金流量净额：</t>
         </is>
@@ -6646,13 +6660,13 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="5" t="inlineStr">
+      <c r="A502" s="28" t="inlineStr">
         <is>
           <t>2.不涉及现金收支的重大投资和筹资活动：</t>
         </is>
       </c>
-      <c r="B502" s="13" t="inlineStr"/>
-      <c r="C502" s="15" t="inlineStr"/>
+      <c r="B502" s="18" t="inlineStr"/>
+      <c r="C502" s="19" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="5" t="inlineStr">
@@ -6660,8 +6674,8 @@
           <t>债务转为资本</t>
         </is>
       </c>
-      <c r="B503" s="13" t="inlineStr"/>
-      <c r="C503" s="15" t="inlineStr"/>
+      <c r="B503" s="18" t="inlineStr"/>
+      <c r="C503" s="19" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="5" t="inlineStr">
@@ -6669,8 +6683,8 @@
           <t>一年内到期的可转换公司债券</t>
         </is>
       </c>
-      <c r="B504" s="13" t="inlineStr"/>
-      <c r="C504" s="15" t="inlineStr"/>
+      <c r="B504" s="18" t="inlineStr"/>
+      <c r="C504" s="19" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="5" t="inlineStr">
@@ -6678,17 +6692,17 @@
           <t>融资租入固定资产</t>
         </is>
       </c>
-      <c r="B505" s="13" t="inlineStr"/>
-      <c r="C505" s="15" t="inlineStr"/>
+      <c r="B505" s="18" t="inlineStr"/>
+      <c r="C505" s="19" t="inlineStr"/>
     </row>
     <row r="506">
-      <c r="A506" s="5" t="inlineStr">
+      <c r="A506" s="28" t="inlineStr">
         <is>
           <t>3.现金及现金等价物净变动情况：</t>
         </is>
       </c>
-      <c r="B506" s="13" t="inlineStr"/>
-      <c r="C506" s="15" t="inlineStr"/>
+      <c r="B506" s="18" t="inlineStr"/>
+      <c r="C506" s="19" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="5" t="inlineStr">
@@ -6722,8 +6736,8 @@
           <t>加：现金等价物的期末余额</t>
         </is>
       </c>
-      <c r="B509" s="13" t="inlineStr"/>
-      <c r="C509" s="15" t="inlineStr"/>
+      <c r="B509" s="18" t="inlineStr"/>
+      <c r="C509" s="19" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="5" t="inlineStr">
@@ -6731,19 +6745,19 @@
           <t>减：现金等价物的期初余额</t>
         </is>
       </c>
-      <c r="B510" s="13" t="inlineStr"/>
-      <c r="C510" s="15" t="inlineStr"/>
+      <c r="B510" s="18" t="inlineStr"/>
+      <c r="C510" s="19" t="inlineStr"/>
     </row>
     <row r="511">
-      <c r="A511" s="8" t="inlineStr">
+      <c r="A511" s="29" t="inlineStr">
         <is>
           <t>现金及现金等价物净增加额</t>
         </is>
       </c>
-      <c r="B511" s="9" t="n">
+      <c r="B511" s="30" t="n">
         <v>-65613.81</v>
       </c>
-      <c r="C511" s="10" t="n">
+      <c r="C511" s="31" t="n">
         <v>-132025.68</v>
       </c>
     </row>
@@ -6803,8 +6817,8 @@
           <t>可随时用于支付的银行存款</t>
         </is>
       </c>
-      <c r="B517" s="13" t="inlineStr"/>
-      <c r="C517" s="15" t="inlineStr"/>
+      <c r="B517" s="18" t="inlineStr"/>
+      <c r="C517" s="19" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="5" t="inlineStr">
@@ -6812,19 +6826,19 @@
           <t>3个月内可用于支付的其他货币资金</t>
         </is>
       </c>
-      <c r="B518" s="13" t="inlineStr"/>
-      <c r="C518" s="15" t="inlineStr"/>
+      <c r="B518" s="18" t="inlineStr"/>
+      <c r="C518" s="19" t="inlineStr"/>
     </row>
     <row r="519">
-      <c r="A519" s="8" t="inlineStr">
+      <c r="A519" s="29" t="inlineStr">
         <is>
           <t>二、现金等价物</t>
         </is>
       </c>
-      <c r="B519" s="9" t="n">
+      <c r="B519" s="30" t="n">
         <v>27133.74</v>
       </c>
-      <c r="C519" s="10" t="n">
+      <c r="C519" s="31" t="n">
         <v>92747.55</v>
       </c>
     </row>
@@ -6883,28 +6897,28 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="8" t="inlineStr">
+      <c r="A525" s="29" t="inlineStr">
         <is>
           <t>深圳市一方保成科技有限公司</t>
         </is>
       </c>
-      <c r="B525" s="19" t="inlineStr">
+      <c r="B525" s="21" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="C525" s="19" t="inlineStr">
+      <c r="C525" s="21" t="inlineStr">
         <is>
           <t>软件和信息技术服务业</t>
         </is>
       </c>
-      <c r="D525" s="18" t="n">
+      <c r="D525" s="40" t="n">
         <v>1000</v>
       </c>
-      <c r="E525" s="18" t="n">
+      <c r="E525" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="F525" s="24" t="n">
+      <c r="F525" s="41" t="n">
         <v>100</v>
       </c>
     </row>
@@ -6952,9 +6966,9 @@
     </row>
     <row r="530">
       <c r="A530" s="16" t="n"/>
-      <c r="B530" s="25" t="n"/>
-      <c r="C530" s="25" t="n"/>
-      <c r="D530" s="25" t="n"/>
+      <c r="B530" s="37" t="n"/>
+      <c r="C530" s="37" t="n"/>
+      <c r="D530" s="37" t="n"/>
       <c r="E530" s="13" t="inlineStr">
         <is>
           <t>直接</t>
@@ -6967,28 +6981,28 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="8" t="inlineStr">
+      <c r="A531" s="29" t="inlineStr">
         <is>
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B531" s="19" t="inlineStr">
+      <c r="B531" s="21" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="C531" s="19" t="inlineStr">
+      <c r="C531" s="21" t="inlineStr">
         <is>
           <t>软件和信息技术服务业</t>
         </is>
       </c>
-      <c r="D531" s="18" t="n">
+      <c r="D531" s="40" t="n">
         <v>2000</v>
       </c>
-      <c r="E531" s="18" t="n">
+      <c r="E531" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="F531" s="24" t="n">
+      <c r="F531" s="41" t="n">
         <v>100</v>
       </c>
     </row>
@@ -7000,12 +7014,12 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="2" t="inlineStr">
+      <c r="A534" s="32" t="inlineStr">
         <is>
           <t>关联方名称</t>
         </is>
       </c>
-      <c r="B534" s="4" t="inlineStr">
+      <c r="B534" s="34" t="inlineStr">
         <is>
           <t>与本公司关系</t>
         </is>
@@ -7017,7 +7031,7 @@
           <t>深圳市前海一方科技研发集团有限公司</t>
         </is>
       </c>
-      <c r="B535" s="15" t="inlineStr">
+      <c r="B535" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7029,7 +7043,7 @@
           <t>深圳市前海一方恒融商业保理有限公司</t>
         </is>
       </c>
-      <c r="B536" s="15" t="inlineStr">
+      <c r="B536" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7041,7 +7055,7 @@
           <t>深圳市一方融合咨询管理有限公司</t>
         </is>
       </c>
-      <c r="B537" s="15" t="inlineStr">
+      <c r="B537" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7053,7 +7067,7 @@
           <t>深圳市前海一方实业咨询有限公司</t>
         </is>
       </c>
-      <c r="B538" s="15" t="inlineStr">
+      <c r="B538" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7065,7 +7079,7 @@
           <t>深圳市方荣企业管理有限公司</t>
         </is>
       </c>
-      <c r="B539" s="15" t="inlineStr">
+      <c r="B539" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7077,7 +7091,7 @@
           <t>深圳市元旸科技有限公司</t>
         </is>
       </c>
-      <c r="B540" s="15" t="inlineStr">
+      <c r="B540" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7089,7 +7103,7 @@
           <t>泉州市元旸科技有限公司</t>
         </is>
       </c>
-      <c r="B541" s="15" t="inlineStr">
+      <c r="B541" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7101,7 +7115,7 @@
           <t>北京一方商业保理有限公司</t>
         </is>
       </c>
-      <c r="B542" s="15" t="inlineStr">
+      <c r="B542" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7113,7 +7127,7 @@
           <t>江苏华美一方供应链数字科技有限公司</t>
         </is>
       </c>
-      <c r="B543" s="15" t="inlineStr">
+      <c r="B543" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7125,7 +7139,7 @@
           <t>成都天投恒融商业保理有限公司</t>
         </is>
       </c>
-      <c r="B544" s="15" t="inlineStr">
+      <c r="B544" s="19" t="inlineStr">
         <is>
           <t>公司所属企业集团的其他成员单位的联营企业</t>
         </is>
@@ -7137,7 +7151,7 @@
           <t>成都天投恒融供应链服务有限公司</t>
         </is>
       </c>
-      <c r="B545" s="15" t="inlineStr">
+      <c r="B545" s="19" t="inlineStr">
         <is>
           <t>公司所属企业集团的其他成员单位的联营企业</t>
         </is>
@@ -7149,7 +7163,7 @@
           <t>浙江承信数字科技有限公司</t>
         </is>
       </c>
-      <c r="B546" s="15" t="inlineStr">
+      <c r="B546" s="19" t="inlineStr">
         <is>
           <t>公司所属企业集团的其他成员单位的联营企业</t>
         </is>
@@ -7161,7 +7175,7 @@
           <t>深圳市稳诚一方数字科技服务有限公司</t>
         </is>
       </c>
-      <c r="B547" s="15" t="inlineStr">
+      <c r="B547" s="19" t="inlineStr">
         <is>
           <t>公司所属企业集团的其他成员单位的联营企业</t>
         </is>
@@ -7173,7 +7187,7 @@
           <t>浙江华域天成科技服务有限公司</t>
         </is>
       </c>
-      <c r="B548" s="15" t="inlineStr">
+      <c r="B548" s="19" t="inlineStr">
         <is>
           <t>公司所属企业集团的其他成员单位的联营企业</t>
         </is>
@@ -7185,7 +7199,7 @@
           <t>豆方数科（深圳）有限责任公司</t>
         </is>
       </c>
-      <c r="B549" s="15" t="inlineStr">
+      <c r="B549" s="19" t="inlineStr">
         <is>
           <t>公司所属企业集团的其他成员单位的联营企业</t>
         </is>
@@ -7197,7 +7211,7 @@
           <t>深圳市海河智融科技有限责任公司</t>
         </is>
       </c>
-      <c r="B550" s="15" t="inlineStr">
+      <c r="B550" s="19" t="inlineStr">
         <is>
           <t>公司所属企业集团的其他成员单位的联营企业（2025年07月31日已注销）</t>
         </is>
@@ -7209,7 +7223,7 @@
           <t>江苏常链一方数字供应链科技有限公司</t>
         </is>
       </c>
-      <c r="B551" s="15" t="inlineStr">
+      <c r="B551" s="19" t="inlineStr">
         <is>
           <t>公司所属企业集团的其他成员单位的联营企业</t>
         </is>
@@ -7221,7 +7235,7 @@
           <t>深圳市前海一方供应链管理有限公司</t>
         </is>
       </c>
-      <c r="B552" s="15" t="inlineStr">
+      <c r="B552" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7233,7 +7247,7 @@
           <t>佛山市友阳供应链管理有限公司</t>
         </is>
       </c>
-      <c r="B553" s="15" t="inlineStr">
+      <c r="B553" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7245,7 +7259,7 @@
           <t>深圳市隆富投资发展有限公司</t>
         </is>
       </c>
-      <c r="B554" s="15" t="inlineStr">
+      <c r="B554" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7257,7 +7271,7 @@
           <t>恒荣投资（新丰）有限公司</t>
         </is>
       </c>
-      <c r="B555" s="15" t="inlineStr">
+      <c r="B555" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7269,7 +7283,7 @@
           <t>深圳市华丽商贸物流有限公司</t>
         </is>
       </c>
-      <c r="B556" s="15" t="inlineStr">
+      <c r="B556" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7281,7 +7295,7 @@
           <t>深圳市恒荣财务信息咨询有限公司</t>
         </is>
       </c>
-      <c r="B557" s="15" t="inlineStr">
+      <c r="B557" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7293,7 +7307,7 @@
           <t>深圳市恒荣科技信息咨询服务有限公司</t>
         </is>
       </c>
-      <c r="B558" s="15" t="inlineStr">
+      <c r="B558" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7305,7 +7319,7 @@
           <t>深圳市恒荣电子咨询服务有限公司</t>
         </is>
       </c>
-      <c r="B559" s="15" t="inlineStr">
+      <c r="B559" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7317,7 +7331,7 @@
           <t>深圳市荣业矿业有限公司</t>
         </is>
       </c>
-      <c r="B560" s="15" t="inlineStr">
+      <c r="B560" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7329,7 +7343,7 @@
           <t>始兴恒荣森林旅游开发有限公司</t>
         </is>
       </c>
-      <c r="B561" s="15" t="inlineStr">
+      <c r="B561" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7341,7 +7355,7 @@
           <t>深圳市融恒新材料有限公司</t>
         </is>
       </c>
-      <c r="B562" s="15" t="inlineStr">
+      <c r="B562" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7353,7 +7367,7 @@
           <t>深圳市融富实业有限公司</t>
         </is>
       </c>
-      <c r="B563" s="15" t="inlineStr">
+      <c r="B563" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7365,7 +7379,7 @@
           <t>前海一方（大连）石油化工有限公司</t>
         </is>
       </c>
-      <c r="B564" s="15" t="inlineStr">
+      <c r="B564" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7377,7 +7391,7 @@
           <t>深圳市彩虹电子有限公司</t>
         </is>
       </c>
-      <c r="B565" s="15" t="inlineStr">
+      <c r="B565" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7389,7 +7403,7 @@
           <t>深圳市恒荣置业有限公司</t>
         </is>
       </c>
-      <c r="B566" s="15" t="inlineStr">
+      <c r="B566" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7401,7 +7415,7 @@
           <t>恒荣矿业（新丰）有限公司</t>
         </is>
       </c>
-      <c r="B567" s="15" t="inlineStr">
+      <c r="B567" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7413,7 +7427,7 @@
           <t>深圳晸信投资管理有限公司</t>
         </is>
       </c>
-      <c r="B568" s="15" t="inlineStr">
+      <c r="B568" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7425,7 +7439,7 @@
           <t>唐山市天恒建材有限公司</t>
         </is>
       </c>
-      <c r="B569" s="15" t="inlineStr">
+      <c r="B569" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7437,7 +7451,7 @@
           <t>深圳市霖梓投资发展有限公司</t>
         </is>
       </c>
-      <c r="B570" s="15" t="inlineStr">
+      <c r="B570" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7449,7 +7463,7 @@
           <t>深圳市恒荣置地有限公司</t>
         </is>
       </c>
-      <c r="B571" s="15" t="inlineStr">
+      <c r="B571" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7461,7 +7475,7 @@
           <t>珠海市恒荣物业服务有限公司</t>
         </is>
       </c>
-      <c r="B572" s="15" t="inlineStr">
+      <c r="B572" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7473,7 +7487,7 @@
           <t>深圳市恒荣物业服务有限公司</t>
         </is>
       </c>
-      <c r="B573" s="15" t="inlineStr">
+      <c r="B573" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7485,7 +7499,7 @@
           <t>唐山市唐城物业服务有限公司</t>
         </is>
       </c>
-      <c r="B574" s="15" t="inlineStr">
+      <c r="B574" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7497,7 +7511,7 @@
           <t>深圳中兴实业股份有限公司</t>
         </is>
       </c>
-      <c r="B575" s="15" t="inlineStr">
+      <c r="B575" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7509,7 +7523,7 @@
           <t>东莞市恒荣置地有限公司</t>
         </is>
       </c>
-      <c r="B576" s="15" t="inlineStr">
+      <c r="B576" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7521,19 +7535,19 @@
           <t>广东华汇矿业有限公司</t>
         </is>
       </c>
-      <c r="B577" s="15" t="inlineStr">
+      <c r="B577" s="19" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="8" t="inlineStr">
+      <c r="A578" s="29" t="inlineStr">
         <is>
           <t>深圳市合恒实业有限公司</t>
         </is>
       </c>
-      <c r="B578" s="21" t="inlineStr">
+      <c r="B578" s="24" t="inlineStr">
         <is>
           <t>公司实际控制人控制的其他企业</t>
         </is>
@@ -7547,24 +7561,24 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="2" t="inlineStr">
+      <c r="A581" s="32" t="inlineStr">
         <is>
           <t>关联方名称</t>
         </is>
       </c>
-      <c r="B581" s="4" t="inlineStr">
+      <c r="B581" s="34" t="inlineStr">
         <is>
           <t>与本公司关系</t>
         </is>
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="8" t="inlineStr">
+      <c r="A582" s="29" t="inlineStr">
         <is>
           <t>柏金</t>
         </is>
       </c>
-      <c r="B582" s="21" t="inlineStr">
+      <c r="B582" s="24" t="inlineStr">
         <is>
           <t>公司法定代表人</t>
         </is>
@@ -7612,12 +7626,12 @@
           <t>深圳市前海一方恒融商业保理有限公司</t>
         </is>
       </c>
-      <c r="B587" s="13" t="inlineStr">
+      <c r="B587" s="18" t="inlineStr">
         <is>
           <t>提供服务（技术）</t>
         </is>
       </c>
-      <c r="C587" s="13" t="inlineStr">
+      <c r="C587" s="18" t="inlineStr">
         <is>
           <t>软件服务</t>
         </is>
@@ -7632,12 +7646,12 @@
           <t>豆方数科（深圳）有限责任公司</t>
         </is>
       </c>
-      <c r="B588" s="13" t="inlineStr">
+      <c r="B588" s="18" t="inlineStr">
         <is>
           <t>提供服务（技术）</t>
         </is>
       </c>
-      <c r="C588" s="13" t="inlineStr">
+      <c r="C588" s="18" t="inlineStr">
         <is>
           <t>咨询服务</t>
         </is>
@@ -7647,22 +7661,22 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="8" t="inlineStr">
+      <c r="A589" s="29" t="inlineStr">
         <is>
           <t>江苏华美一方供应链数字科技有限公司</t>
         </is>
       </c>
-      <c r="B589" s="19" t="inlineStr">
+      <c r="B589" s="21" t="inlineStr">
         <is>
           <t>提供服务（技术）</t>
         </is>
       </c>
-      <c r="C589" s="19" t="inlineStr">
+      <c r="C589" s="21" t="inlineStr">
         <is>
           <t>咨询服务</t>
         </is>
       </c>
-      <c r="D589" s="10" t="n">
+      <c r="D589" s="31" t="n">
         <v>3981359.08</v>
       </c>
     </row>
@@ -7681,32 +7695,32 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="2" t="inlineStr">
+      <c r="A593" s="32" t="inlineStr">
         <is>
           <t>被担保方</t>
         </is>
       </c>
-      <c r="B593" s="3" t="inlineStr">
+      <c r="B593" s="33" t="inlineStr">
         <is>
           <t>担保方式</t>
         </is>
       </c>
-      <c r="C593" s="3" t="inlineStr">
+      <c r="C593" s="33" t="inlineStr">
         <is>
           <t>币别</t>
         </is>
       </c>
-      <c r="D593" s="3" t="inlineStr">
+      <c r="D593" s="33" t="inlineStr">
         <is>
           <t>担保金额</t>
         </is>
       </c>
-      <c r="E593" s="3" t="inlineStr">
+      <c r="E593" s="33" t="inlineStr">
         <is>
           <t>担保到期日</t>
         </is>
       </c>
-      <c r="F593" s="4" t="inlineStr">
+      <c r="F593" s="34" t="inlineStr">
         <is>
           <t>担保合同编号</t>
         </is>
@@ -7718,12 +7732,12 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B594" s="13" t="inlineStr">
+      <c r="B594" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C594" s="13" t="inlineStr">
+      <c r="C594" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
@@ -7731,12 +7745,12 @@
       <c r="D594" s="6" t="n">
         <v>1776803.62</v>
       </c>
-      <c r="E594" s="13" t="inlineStr">
+      <c r="E594" s="18" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="F594" s="15" t="inlineStr">
+      <c r="F594" s="19" t="inlineStr">
         <is>
           <t>B11115840H0001GT2506058000290</t>
         </is>
@@ -7748,12 +7762,12 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B595" s="13" t="inlineStr">
+      <c r="B595" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C595" s="13" t="inlineStr">
+      <c r="C595" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
@@ -7761,12 +7775,12 @@
       <c r="D595" s="6" t="n">
         <v>1056062.95</v>
       </c>
-      <c r="E595" s="13" t="inlineStr">
+      <c r="E595" s="18" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
       </c>
-      <c r="F595" s="15" t="inlineStr">
+      <c r="F595" s="19" t="inlineStr">
         <is>
           <t>B11115840H0001GT2506058000290</t>
         </is>
@@ -7778,12 +7792,12 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B596" s="13" t="inlineStr">
+      <c r="B596" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C596" s="13" t="inlineStr">
+      <c r="C596" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
@@ -7791,12 +7805,12 @@
       <c r="D596" s="6" t="n">
         <v>1055099.65</v>
       </c>
-      <c r="E596" s="13" t="inlineStr">
+      <c r="E596" s="18" t="inlineStr">
         <is>
           <t>2026-11-14</t>
         </is>
       </c>
-      <c r="F596" s="15" t="inlineStr">
+      <c r="F596" s="19" t="inlineStr">
         <is>
           <t>B1111584OH0001GT2506058000290</t>
         </is>
@@ -7808,12 +7822,12 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B597" s="13" t="inlineStr">
+      <c r="B597" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C597" s="13" t="inlineStr">
+      <c r="C597" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
@@ -7821,12 +7835,12 @@
       <c r="D597" s="6" t="n">
         <v>1042750.98</v>
       </c>
-      <c r="E597" s="13" t="inlineStr">
+      <c r="E597" s="18" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="F597" s="15" t="inlineStr">
+      <c r="F597" s="19" t="inlineStr">
         <is>
           <t>B1111584OHO001GT2506058000290</t>
         </is>
@@ -7838,12 +7852,12 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B598" s="13" t="inlineStr">
+      <c r="B598" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C598" s="13" t="inlineStr">
+      <c r="C598" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
@@ -7851,12 +7865,12 @@
       <c r="D598" s="6" t="n">
         <v>914169.2</v>
       </c>
-      <c r="E598" s="13" t="inlineStr">
+      <c r="E598" s="18" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F598" s="15" t="inlineStr">
+      <c r="F598" s="19" t="inlineStr">
         <is>
           <t>B11115840H0001GT2506058000290</t>
         </is>
@@ -7868,12 +7882,12 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B599" s="13" t="inlineStr">
+      <c r="B599" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C599" s="13" t="inlineStr">
+      <c r="C599" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
@@ -7881,12 +7895,12 @@
       <c r="D599" s="6" t="n">
         <v>846285.38</v>
       </c>
-      <c r="E599" s="13" t="inlineStr">
+      <c r="E599" s="18" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="F599" s="15" t="inlineStr">
+      <c r="F599" s="19" t="inlineStr">
         <is>
           <t>B11115840H0001GT2506058000290</t>
         </is>
@@ -7898,12 +7912,12 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B600" s="13" t="inlineStr">
+      <c r="B600" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C600" s="13" t="inlineStr">
+      <c r="C600" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
@@ -7911,12 +7925,12 @@
       <c r="D600" s="6" t="n">
         <v>843155.4399999999</v>
       </c>
-      <c r="E600" s="13" t="inlineStr">
+      <c r="E600" s="18" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="F600" s="15" t="inlineStr">
+      <c r="F600" s="19" t="inlineStr">
         <is>
           <t>B1111584OHO001GT2506058000290</t>
         </is>
@@ -7928,12 +7942,12 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B601" s="13" t="inlineStr">
+      <c r="B601" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C601" s="13" t="inlineStr">
+      <c r="C601" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
@@ -7941,12 +7955,12 @@
       <c r="D601" s="6" t="n">
         <v>777700.96</v>
       </c>
-      <c r="E601" s="13" t="inlineStr">
+      <c r="E601" s="18" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F601" s="15" t="inlineStr">
+      <c r="F601" s="19" t="inlineStr">
         <is>
           <t>B1111584OHO001GT2506058000290</t>
         </is>
@@ -7958,25 +7972,25 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B602" s="13" t="inlineStr">
+      <c r="B602" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C602" s="13" t="inlineStr">
+      <c r="C602" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
       </c>
-      <c r="D602" s="20" t="n">
+      <c r="D602" s="22" t="n">
         <v>52000</v>
       </c>
-      <c r="E602" s="13" t="inlineStr">
+      <c r="E602" s="18" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F602" s="15" t="inlineStr">
+      <c r="F602" s="19" t="inlineStr">
         <is>
           <t>B1111584OH0001GT2506058000290</t>
         </is>
@@ -7988,25 +8002,25 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B603" s="13" t="inlineStr">
+      <c r="B603" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C603" s="13" t="inlineStr">
+      <c r="C603" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
       </c>
-      <c r="D603" s="20" t="n">
+      <c r="D603" s="22" t="n">
         <v>26000</v>
       </c>
-      <c r="E603" s="13" t="inlineStr">
+      <c r="E603" s="18" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="F603" s="15" t="inlineStr">
+      <c r="F603" s="19" t="inlineStr">
         <is>
           <t>B1111584OH0001GT2506058000290</t>
         </is>
@@ -8018,25 +8032,25 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B604" s="13" t="inlineStr">
+      <c r="B604" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C604" s="13" t="inlineStr">
+      <c r="C604" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
       </c>
-      <c r="D604" s="20" t="n">
+      <c r="D604" s="22" t="n">
         <v>26000</v>
       </c>
-      <c r="E604" s="13" t="inlineStr">
+      <c r="E604" s="18" t="inlineStr">
         <is>
           <t>2026-09.25</t>
         </is>
       </c>
-      <c r="F604" s="15" t="inlineStr">
+      <c r="F604" s="19" t="inlineStr">
         <is>
           <t>B1111584OH0001GT2506058000290</t>
         </is>
@@ -8048,25 +8062,25 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B605" s="13" t="inlineStr">
+      <c r="B605" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C605" s="13" t="inlineStr">
+      <c r="C605" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
       </c>
-      <c r="D605" s="20" t="n">
+      <c r="D605" s="22" t="n">
         <v>26000</v>
       </c>
-      <c r="E605" s="13" t="inlineStr">
+      <c r="E605" s="18" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="F605" s="15" t="inlineStr">
+      <c r="F605" s="19" t="inlineStr">
         <is>
           <t>B11115840H0001GT2506058000290</t>
         </is>
@@ -8078,25 +8092,25 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B606" s="13" t="inlineStr">
+      <c r="B606" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C606" s="13" t="inlineStr">
+      <c r="C606" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
       </c>
-      <c r="D606" s="20" t="n">
+      <c r="D606" s="22" t="n">
         <v>26000</v>
       </c>
-      <c r="E606" s="13" t="inlineStr">
+      <c r="E606" s="18" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="F606" s="15" t="inlineStr">
+      <c r="F606" s="19" t="inlineStr">
         <is>
           <t>B11115840H0001GT2506058000290</t>
         </is>
@@ -8108,12 +8122,12 @@
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B607" s="13" t="inlineStr">
+      <c r="B607" s="18" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C607" s="13" t="inlineStr">
+      <c r="C607" s="18" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
@@ -8121,42 +8135,42 @@
       <c r="D607" s="6" t="n">
         <v>25681.23</v>
       </c>
-      <c r="E607" s="13" t="inlineStr">
+      <c r="E607" s="18" t="inlineStr">
         <is>
           <t>2026-12-30</t>
         </is>
       </c>
-      <c r="F607" s="15" t="inlineStr">
+      <c r="F607" s="19" t="inlineStr">
         <is>
           <t>B1111584OH0001GT2506058000290</t>
         </is>
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="8" t="inlineStr">
+      <c r="A608" s="29" t="inlineStr">
         <is>
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="B608" s="19" t="inlineStr">
+      <c r="B608" s="21" t="inlineStr">
         <is>
           <t>最高额担保</t>
         </is>
       </c>
-      <c r="C608" s="19" t="inlineStr">
+      <c r="C608" s="21" t="inlineStr">
         <is>
           <t>人民币</t>
         </is>
       </c>
-      <c r="D608" s="9" t="n">
+      <c r="D608" s="30" t="n">
         <v>24804.6</v>
       </c>
-      <c r="E608" s="19" t="inlineStr">
+      <c r="E608" s="21" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F608" s="21" t="inlineStr">
+      <c r="F608" s="24" t="inlineStr">
         <is>
           <t>B1111584OH0001GT2506058000290</t>
         </is>
@@ -8192,7 +8206,7 @@
           <t>应收账款</t>
         </is>
       </c>
-      <c r="B612" s="13" t="inlineStr">
+      <c r="B612" s="18" t="inlineStr">
         <is>
           <t>豆方数科（深圳）有限责任公司</t>
         </is>
@@ -8207,7 +8221,7 @@
           <t>应收账款</t>
         </is>
       </c>
-      <c r="B613" s="13" t="inlineStr">
+      <c r="B613" s="18" t="inlineStr">
         <is>
           <t>江苏华美一方供应链数字科技有限公司</t>
         </is>
@@ -8222,12 +8236,12 @@
           <t>预付账款</t>
         </is>
       </c>
-      <c r="B614" s="13" t="inlineStr">
+      <c r="B614" s="18" t="inlineStr">
         <is>
           <t>成都思致科技有限公司</t>
         </is>
       </c>
-      <c r="C614" s="23" t="n">
+      <c r="C614" s="26" t="n">
         <v>4034920</v>
       </c>
     </row>
@@ -8237,7 +8251,7 @@
           <t>合同负债</t>
         </is>
       </c>
-      <c r="B615" s="13" t="inlineStr">
+      <c r="B615" s="18" t="inlineStr">
         <is>
           <t>深圳市前海一方恒融商业保理有限公司</t>
         </is>
@@ -8252,7 +8266,7 @@
           <t>其他应付款</t>
         </is>
       </c>
-      <c r="B616" s="13" t="inlineStr">
+      <c r="B616" s="18" t="inlineStr">
         <is>
           <t>深圳市前海一方科技研发集团有限公司</t>
         </is>
@@ -8262,17 +8276,17 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="8" t="inlineStr">
+      <c r="A617" s="29" t="inlineStr">
         <is>
           <t>其他应付款</t>
         </is>
       </c>
-      <c r="B617" s="19" t="inlineStr">
+      <c r="B617" s="21" t="inlineStr">
         <is>
           <t>深圳市前海一方恒融商业保理有限公司</t>
         </is>
       </c>
-      <c r="C617" s="10" t="n">
+      <c r="C617" s="31" t="n">
         <v>3770036.02</v>
       </c>
     </row>
@@ -8328,19 +8342,19 @@
       <c r="A627" t="inlineStr"/>
     </row>
     <row r="628">
-      <c r="A628" s="28" t="inlineStr">
+      <c r="A628" s="42" t="inlineStr">
         <is>
           <t>法定代表人</t>
         </is>
       </c>
-      <c r="B628" s="29" t="inlineStr"/>
-      <c r="C628" s="29" t="inlineStr">
+      <c r="B628" s="43" t="inlineStr"/>
+      <c r="C628" s="43" t="inlineStr">
         <is>
           <t>主管会计工作负责人</t>
         </is>
       </c>
-      <c r="D628" s="29" t="inlineStr"/>
-      <c r="E628" s="30" t="inlineStr">
+      <c r="D628" s="43" t="inlineStr"/>
+      <c r="E628" s="44" t="inlineStr">
         <is>
           <t>会计机构负责人</t>
         </is>
